--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROPORSI PERTANIAN NON PERTANIA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROPORSI PERTANIAN NON PERTANIA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,247 +417,247 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha SE2026</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Jumlah UTP Subsektor Target (ST2023)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Pertanian</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Persentase Pertanian</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Non Pertanian</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>USAHA BARU - Pertanian​</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>USAHA BARU - Persentase Pertanian​</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>USAHA BARU - Non Pertanian​</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Pertanian​​</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Persentase Pertanian​​</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Non Pertanian​​</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Pertanian​​​</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Persentase Pertanian​​​</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Non Pertanian​​​</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>
@@ -749,13 +737,13 @@
         <v>70</v>
       </c>
       <c r="U2" t="n">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="V2" t="n">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="W2" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
         <v>3</v>
@@ -764,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -773,31 +761,31 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="AF2" t="n">
-        <v>343</v>
+        <v>393</v>
       </c>
       <c r="AG2" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AH2" t="n">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="AI2" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AK2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -809,16 +797,16 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="AR2" t="n">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="AS2" t="n">
         <v>364</v>
@@ -1071,10 +1059,10 @@
         <v>33</v>
       </c>
       <c r="U4" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="V4" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1083,7 +1071,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1095,7 +1083,7 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1104,13 +1092,13 @@
         <v>429</v>
       </c>
       <c r="AF4" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="AG4" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="AH4" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1119,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1131,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -1140,7 +1128,7 @@
         <v>429</v>
       </c>
       <c r="AR4" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="AS4" t="n">
         <v>363</v>
@@ -1235,7 +1223,7 @@
         <v>219</v>
       </c>
       <c r="V5" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1256,10 +1244,10 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>425</v>
@@ -1271,7 +1259,7 @@
         <v>219</v>
       </c>
       <c r="AH5" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1292,10 +1280,10 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
         <v>425</v>
@@ -1393,16 +1381,16 @@
         <v>13</v>
       </c>
       <c r="U6" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="V6" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1417,28 +1405,28 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AF6" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AG6" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AH6" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1453,16 +1441,16 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AR6" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AS6" t="n">
         <v>354</v>
@@ -1554,13 +1542,13 @@
         <v>34</v>
       </c>
       <c r="U7" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="V7" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1584,19 +1572,19 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AF7" t="n">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="AG7" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="AH7" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="AI7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -1620,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AR7" t="n">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="AS7" t="n">
         <v>336</v>
@@ -1715,16 +1703,16 @@
         <v>14</v>
       </c>
       <c r="U8" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="V8" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1745,22 +1733,22 @@
         <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="AF8" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="AG8" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="AH8" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1781,10 +1769,10 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="AR8" t="n">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="AS8" t="n">
         <v>304</v>
@@ -1876,13 +1864,13 @@
         <v>37</v>
       </c>
       <c r="U9" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="V9" t="n">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1906,19 +1894,19 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AF9" t="n">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="AG9" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="AH9" t="n">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="AI9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
@@ -1942,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AR9" t="n">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="AS9" t="n">
         <v>288</v>
@@ -2040,16 +2028,16 @@
         <v>186</v>
       </c>
       <c r="V10" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="W10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>7</v>
       </c>
       <c r="Y10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2076,16 +2064,16 @@
         <v>186</v>
       </c>
       <c r="AH10" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="AI10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
         <v>7</v>
       </c>
       <c r="AK10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2198,19 +2186,19 @@
         <v>21</v>
       </c>
       <c r="U11" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="V11" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="W11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2222,31 +2210,31 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>407</v>
       </c>
       <c r="AF11" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AG11" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="AH11" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2258,16 +2246,16 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AP11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
         <v>407</v>
       </c>
       <c r="AR11" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AS11" t="n">
         <v>373</v>
@@ -2359,13 +2347,13 @@
         <v>52</v>
       </c>
       <c r="U12" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="V12" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="W12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
@@ -2383,25 +2371,25 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AF12" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AG12" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AH12" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AI12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
         <v>1</v>
@@ -2419,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AR12" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AS12" t="n">
         <v>383</v>
@@ -2520,13 +2508,13 @@
         <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="V13" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2550,19 +2538,19 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AF13" t="n">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="AG13" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="AH13" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="AI13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -2586,10 +2574,10 @@
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AR13" t="n">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="AS13" t="n">
         <v>373</v>
@@ -2681,16 +2669,16 @@
         <v>59</v>
       </c>
       <c r="U14" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="V14" t="n">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="W14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2714,19 +2702,19 @@
         <v>426</v>
       </c>
       <c r="AF14" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="AG14" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AH14" t="n">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="AI14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2750,7 +2738,7 @@
         <v>426</v>
       </c>
       <c r="AR14" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="AS14" t="n">
         <v>364</v>
@@ -2842,13 +2830,13 @@
         <v>87</v>
       </c>
       <c r="U15" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="V15" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="W15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
@@ -2866,25 +2854,25 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AF15" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AG15" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="AH15" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="AI15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AJ15" t="n">
         <v>1</v>
@@ -2902,16 +2890,16 @@
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AR15" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AS15" t="n">
         <v>324</v>
@@ -3003,13 +2991,13 @@
         <v>27</v>
       </c>
       <c r="U16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="V16" t="n">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="W16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -3018,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -3030,22 +3018,22 @@
         <v>30</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="AF16" t="n">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="AG16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="n">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="AI16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
@@ -3054,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM16" t="n">
         <v>0</v>
@@ -3066,13 +3054,13 @@
         <v>30</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="AR16" t="n">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="AS16" t="n">
         <v>288</v>
@@ -3164,25 +3152,25 @@
         <v>27</v>
       </c>
       <c r="U17" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="V17" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -3194,31 +3182,31 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AF17" t="n">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="AG17" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AH17" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="AI17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AK17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
@@ -3230,10 +3218,10 @@
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AR17" t="n">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="AS17" t="n">
         <v>370</v>
@@ -3325,19 +3313,19 @@
         <v>32</v>
       </c>
       <c r="U18" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="V18" t="n">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="W18" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="X18" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3355,25 +3343,25 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AF18" t="n">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="AG18" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="AI18" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="AJ18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AK18" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3391,10 +3379,10 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AR18" t="n">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AS18" t="n">
         <v>366</v>
@@ -3486,13 +3474,13 @@
         <v>38</v>
       </c>
       <c r="U19" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="V19" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="W19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -3519,16 +3507,16 @@
         <v>454</v>
       </c>
       <c r="AF19" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG19" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AH19" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="AI19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
@@ -3555,7 +3543,7 @@
         <v>454</v>
       </c>
       <c r="AR19" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AS19" t="n">
         <v>423</v>
@@ -3811,10 +3799,10 @@
         <v>186</v>
       </c>
       <c r="V21" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>2</v>
@@ -3832,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3847,10 +3835,10 @@
         <v>186</v>
       </c>
       <c r="AH21" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AI21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
         <v>2</v>
@@ -3868,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AP21" t="n">
         <v>0</v>
@@ -3969,16 +3957,16 @@
         <v>30</v>
       </c>
       <c r="U22" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="V22" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Y22" t="n">
         <v>7</v>
@@ -3999,22 +3987,22 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AF22" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG22" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AH22" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AK22" t="n">
         <v>7</v>
@@ -4035,10 +4023,10 @@
         <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AR22" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AS22" t="n">
         <v>410</v>
@@ -4130,19 +4118,19 @@
         <v>11</v>
       </c>
       <c r="U23" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="V23" t="n">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -4160,25 +4148,25 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AF23" t="n">
+        <v>313</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>220</v>
+      </c>
+      <c r="AH23" t="n">
         <v>296</v>
       </c>
-      <c r="AG23" t="n">
-        <v>236</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>286</v>
-      </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ23" t="n">
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4196,10 +4184,10 @@
         <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AR23" t="n">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="AS23" t="n">
         <v>450</v>
@@ -4291,22 +4279,22 @@
         <v>80</v>
       </c>
       <c r="U24" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="V24" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="W24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -4315,7 +4303,7 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -4324,25 +4312,25 @@
         <v>402</v>
       </c>
       <c r="AF24" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG24" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AH24" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="AI24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AJ24" t="n">
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="AL24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
         <v>0</v>
@@ -4351,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="AP24" t="n">
         <v>0</v>
@@ -4360,7 +4348,7 @@
         <v>402</v>
       </c>
       <c r="AR24" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AS24" t="n">
         <v>359</v>
@@ -4452,13 +4440,13 @@
         <v>52</v>
       </c>
       <c r="U25" t="n">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="V25" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -4482,19 +4470,19 @@
         <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AF25" t="n">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="AG25" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="AH25" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ25" t="n">
         <v>0</v>
@@ -4518,10 +4506,10 @@
         <v>1</v>
       </c>
       <c r="AQ25" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AR25" t="n">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="AS25" t="n">
         <v>308</v>
@@ -4613,25 +4601,25 @@
         <v>51</v>
       </c>
       <c r="U26" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="V26" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="W26" t="n">
+        <v>18</v>
+      </c>
+      <c r="X26" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y26" t="n">
         <v>7</v>
       </c>
-      <c r="X26" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>11</v>
-      </c>
       <c r="Z26" t="n">
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4646,28 +4634,28 @@
         <v>472</v>
       </c>
       <c r="AF26" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG26" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AH26" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AI26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK26" t="n">
         <v>7</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>11</v>
-      </c>
       <c r="AL26" t="n">
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN26" t="n">
         <v>0</v>
@@ -4682,7 +4670,7 @@
         <v>472</v>
       </c>
       <c r="AR26" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AS26" t="n">
         <v>419</v>
@@ -4774,13 +4762,13 @@
         <v>61</v>
       </c>
       <c r="U27" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="V27" t="n">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="W27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -4804,19 +4792,19 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AF27" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="AH27" t="n">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="AI27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
@@ -4840,10 +4828,10 @@
         <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AR27" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="AS27" t="n">
         <v>342</v>
@@ -4935,19 +4923,19 @@
         <v>59</v>
       </c>
       <c r="U28" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="V28" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X28" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4959,31 +4947,31 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AF28" t="n">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="n">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="AH28" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="AI28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ28" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4995,16 +4983,16 @@
         <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AP28" t="n">
         <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AR28" t="n">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="AS28" t="n">
         <v>384</v>
@@ -5096,13 +5084,13 @@
         <v>44</v>
       </c>
       <c r="U29" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="V29" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="W29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -5120,25 +5108,25 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AF29" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="AG29" t="n">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AH29" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="AI29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
@@ -5156,16 +5144,16 @@
         <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AP29" t="n">
         <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AR29" t="n">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="AS29" t="n">
         <v>357</v>
@@ -5257,22 +5245,22 @@
         <v>60</v>
       </c>
       <c r="U30" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="V30" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="W30" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -5281,34 +5269,34 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="AF30" t="n">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="AG30" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AH30" t="n">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ30" t="n">
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
@@ -5323,10 +5311,10 @@
         <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="AR30" t="n">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="AS30" t="n">
         <v>457</v>
@@ -5421,13 +5409,13 @@
         <v>8</v>
       </c>
       <c r="V31" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="W31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="X31" t="n">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -5451,19 +5439,19 @@
         <v>332</v>
       </c>
       <c r="AF31" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="AG31" t="n">
         <v>8</v>
       </c>
       <c r="AH31" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="AI31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AJ31" t="n">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -5487,7 +5475,7 @@
         <v>332</v>
       </c>
       <c r="AR31" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="AS31" t="n">
         <v>315</v>
@@ -5579,19 +5567,19 @@
         <v>25</v>
       </c>
       <c r="U32" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V32" t="n">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="W32" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5603,31 +5591,31 @@
         <v>1</v>
       </c>
       <c r="AC32" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AD32" t="n">
         <v>3</v>
       </c>
       <c r="AE32" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AF32" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG32" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AH32" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="AI32" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="AJ32" t="n">
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5639,16 +5627,16 @@
         <v>1</v>
       </c>
       <c r="AO32" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AP32" t="n">
         <v>3</v>
       </c>
       <c r="AQ32" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AR32" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AS32" t="n">
         <v>308</v>
@@ -5740,19 +5728,19 @@
         <v>50</v>
       </c>
       <c r="U33" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="V33" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="W33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y33" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5764,31 +5752,31 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AF33" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AG33" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AH33" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="AI33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AK33" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5800,16 +5788,16 @@
         <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AP33" t="n">
         <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AR33" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AS33" t="n">
         <v>365</v>
@@ -5901,16 +5889,16 @@
         <v>46</v>
       </c>
       <c r="U34" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="V34" t="n">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -5925,28 +5913,28 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="AF34" t="n">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="AH34" t="n">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="AI34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
@@ -5961,16 +5949,16 @@
         <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AP34" t="n">
         <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="AR34" t="n">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="AS34" t="n">
         <v>410</v>
@@ -6062,13 +6050,13 @@
         <v>34</v>
       </c>
       <c r="U35" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="V35" t="n">
         <v>182</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -6092,19 +6080,19 @@
         <v>1</v>
       </c>
       <c r="AE35" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AF35" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="AG35" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="AH35" t="n">
         <v>182</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ35" t="n">
         <v>0</v>
@@ -6128,10 +6116,10 @@
         <v>1</v>
       </c>
       <c r="AQ35" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AR35" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="AS35" t="n">
         <v>303</v>
@@ -6223,13 +6211,13 @@
         <v>51</v>
       </c>
       <c r="U36" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="V36" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="W36" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -6253,19 +6241,19 @@
         <v>7</v>
       </c>
       <c r="AE36" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AF36" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="AG36" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AH36" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="AI36" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AJ36" t="n">
         <v>0</v>
@@ -6289,10 +6277,10 @@
         <v>7</v>
       </c>
       <c r="AQ36" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AR36" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="AS36" t="n">
         <v>412</v>
@@ -6384,16 +6372,16 @@
         <v>57</v>
       </c>
       <c r="U37" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="V37" t="n">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="W37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -6408,28 +6396,28 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="AF37" t="n">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="AG37" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AH37" t="n">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="AI37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
         <v>0</v>
@@ -6444,16 +6432,16 @@
         <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AP37" t="n">
         <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="AR37" t="n">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="AS37" t="n">
         <v>371</v>
@@ -6545,19 +6533,19 @@
         <v>55</v>
       </c>
       <c r="U38" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="V38" t="n">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="W38" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="X38" t="n">
         <v>2</v>
       </c>
       <c r="Y38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -6575,25 +6563,25 @@
         <v>4</v>
       </c>
       <c r="AE38" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="AF38" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG38" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="AH38" t="n">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="AI38" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="AJ38" t="n">
         <v>2</v>
       </c>
       <c r="AK38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6611,10 +6599,10 @@
         <v>4</v>
       </c>
       <c r="AQ38" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="AR38" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AS38" t="n">
         <v>453</v>
@@ -6706,22 +6694,22 @@
         <v>43</v>
       </c>
       <c r="U39" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="V39" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="W39" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="X39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y39" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>1</v>
@@ -6739,25 +6727,25 @@
         <v>474</v>
       </c>
       <c r="AF39" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AG39" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AH39" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AI39" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AJ39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK39" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AL39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
         <v>1</v>
@@ -6775,7 +6763,7 @@
         <v>474</v>
       </c>
       <c r="AR39" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AS39" t="n">
         <v>445</v>
@@ -6867,19 +6855,19 @@
         <v>27</v>
       </c>
       <c r="U40" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="V40" t="n">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="W40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6897,25 +6885,25 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AF40" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AG40" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="AH40" t="n">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="AI40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AJ40" t="n">
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6933,10 +6921,10 @@
         <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AR40" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AS40" t="n">
         <v>379</v>
@@ -7028,13 +7016,13 @@
         <v>22</v>
       </c>
       <c r="U41" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="V41" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="W41" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -7058,19 +7046,19 @@
         <v>1</v>
       </c>
       <c r="AE41" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AF41" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="AG41" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AH41" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="AI41" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AJ41" t="n">
         <v>0</v>
@@ -7094,10 +7082,10 @@
         <v>1</v>
       </c>
       <c r="AQ41" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AR41" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="AS41" t="n">
         <v>335</v>
@@ -7189,16 +7177,16 @@
         <v>67</v>
       </c>
       <c r="U42" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="V42" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="W42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -7213,28 +7201,28 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE42" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AF42" t="n">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="AG42" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="AH42" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="AI42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AK42" t="n">
         <v>0</v>
@@ -7249,16 +7237,16 @@
         <v>0</v>
       </c>
       <c r="AO42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ42" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AR42" t="n">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="AS42" t="n">
         <v>371</v>
@@ -7350,19 +7338,19 @@
         <v>73</v>
       </c>
       <c r="U43" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="V43" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="W43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -7380,25 +7368,25 @@
         <v>1</v>
       </c>
       <c r="AE43" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AF43" t="n">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="AG43" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="AH43" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="AI43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7416,10 +7404,10 @@
         <v>1</v>
       </c>
       <c r="AQ43" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AR43" t="n">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="AS43" t="n">
         <v>331</v>
@@ -7511,19 +7499,19 @@
         <v>50</v>
       </c>
       <c r="U44" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="V44" t="n">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="W44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -7541,25 +7529,25 @@
         <v>3</v>
       </c>
       <c r="AE44" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AF44" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AG44" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="AH44" t="n">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="AI44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7577,10 +7565,10 @@
         <v>3</v>
       </c>
       <c r="AQ44" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AR44" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AS44" t="n">
         <v>301</v>
@@ -7672,16 +7660,16 @@
         <v>28</v>
       </c>
       <c r="U45" t="n">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="V45" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="W45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="X45" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y45" t="n">
         <v>87</v>
@@ -7702,22 +7690,22 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="AF45" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="AG45" t="n">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="AH45" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="AI45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AJ45" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AK45" t="n">
         <v>0</v>
@@ -7738,10 +7726,10 @@
         <v>0</v>
       </c>
       <c r="AQ45" t="n">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="AR45" t="n">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="AS45" t="n">
         <v>355</v>
@@ -7833,13 +7821,13 @@
         <v>15</v>
       </c>
       <c r="U46" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="V46" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="W46" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="X46" t="n">
         <v>2</v>
@@ -7857,25 +7845,25 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD46" t="n">
         <v>6</v>
       </c>
       <c r="AE46" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AF46" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="AG46" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="AH46" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AI46" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="AJ46" t="n">
         <v>2</v>
@@ -7893,16 +7881,16 @@
         <v>0</v>
       </c>
       <c r="AO46" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AP46" t="n">
         <v>6</v>
       </c>
       <c r="AQ46" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AR46" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="AS46" t="n">
         <v>434</v>
@@ -7997,13 +7985,13 @@
         <v>170</v>
       </c>
       <c r="V47" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Y47" t="n">
         <v>0</v>
@@ -8018,28 +8006,28 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="AF47" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG47" t="n">
         <v>170</v>
       </c>
       <c r="AH47" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AK47" t="n">
         <v>0</v>
@@ -8054,16 +8042,16 @@
         <v>0</v>
       </c>
       <c r="AO47" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AP47" t="n">
         <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="AR47" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AS47" t="n">
         <v>375</v>
@@ -8155,19 +8143,19 @@
         <v>24</v>
       </c>
       <c r="U48" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="V48" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="W48" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="X48" t="n">
         <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
@@ -8179,31 +8167,31 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
+        <v>41</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>414</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>200</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>213</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>134</v>
+      </c>
+      <c r="AI48" t="n">
         <v>24</v>
       </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>413</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>192</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>220</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>145</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>22</v>
-      </c>
       <c r="AJ48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8215,16 +8203,16 @@
         <v>0</v>
       </c>
       <c r="AO48" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="AP48" t="n">
         <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AR48" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="AS48" t="n">
         <v>363</v>
@@ -8319,7 +8307,7 @@
         <v>211</v>
       </c>
       <c r="V49" t="n">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
@@ -8328,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -8340,7 +8328,7 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -8355,10 +8343,10 @@
         <v>211</v>
       </c>
       <c r="AH49" t="n">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="AI49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
         <v>0</v>
@@ -8376,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="AO49" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AP49" t="n">
         <v>0</v>
@@ -8477,19 +8465,19 @@
         <v>56</v>
       </c>
       <c r="U50" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="V50" t="n">
         <v>192</v>
       </c>
       <c r="W50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -8501,7 +8489,7 @@
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AD50" t="n">
         <v>2</v>
@@ -8510,22 +8498,22 @@
         <v>450</v>
       </c>
       <c r="AF50" t="n">
+        <v>226</v>
+      </c>
+      <c r="AG50" t="n">
         <v>224</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>226</v>
       </c>
       <c r="AH50" t="n">
         <v>192</v>
       </c>
       <c r="AI50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ50" t="n">
         <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8537,7 +8525,7 @@
         <v>0</v>
       </c>
       <c r="AO50" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AP50" t="n">
         <v>2</v>
@@ -8546,7 +8534,7 @@
         <v>450</v>
       </c>
       <c r="AR50" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AS50" t="n">
         <v>372</v>
@@ -8638,19 +8626,19 @@
         <v>39</v>
       </c>
       <c r="U51" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="V51" t="n">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="W51" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="X51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -8662,31 +8650,31 @@
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AF51" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="AG51" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="AH51" t="n">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="AI51" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="AJ51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8698,16 +8686,16 @@
         <v>0</v>
       </c>
       <c r="AO51" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="AP51" t="n">
         <v>0</v>
       </c>
       <c r="AQ51" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AR51" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="AS51" t="n">
         <v>395</v>
@@ -8799,13 +8787,13 @@
         <v>47</v>
       </c>
       <c r="U52" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="V52" t="n">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="W52" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
@@ -8823,25 +8811,25 @@
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AD52" t="n">
         <v>1</v>
       </c>
       <c r="AE52" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AF52" t="n">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="AG52" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="AH52" t="n">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="AI52" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AJ52" t="n">
         <v>0</v>
@@ -8859,16 +8847,16 @@
         <v>0</v>
       </c>
       <c r="AO52" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AP52" t="n">
         <v>1</v>
       </c>
       <c r="AQ52" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AR52" t="n">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="AS52" t="n">
         <v>378</v>
@@ -8960,16 +8948,16 @@
         <v>66</v>
       </c>
       <c r="U53" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="V53" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="W53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
@@ -8990,19 +8978,19 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AF53" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="AG53" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="AH53" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AI53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ53" t="n">
         <v>5</v>
@@ -9026,10 +9014,10 @@
         <v>0</v>
       </c>
       <c r="AQ53" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AR53" t="n">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="AS53" t="n">
         <v>429</v>
@@ -9121,16 +9109,16 @@
         <v>15</v>
       </c>
       <c r="U54" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="V54" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y54" t="n">
         <v>22</v>
@@ -9154,19 +9142,19 @@
         <v>424</v>
       </c>
       <c r="AF54" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="AG54" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AH54" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AI54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK54" t="n">
         <v>22</v>
@@ -9190,7 +9178,7 @@
         <v>424</v>
       </c>
       <c r="AR54" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="AS54" t="n">
         <v>396</v>
@@ -9282,25 +9270,25 @@
         <v>61</v>
       </c>
       <c r="U55" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="V55" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="W55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
         <v>1</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB55" t="n">
         <v>0</v>
@@ -9315,28 +9303,28 @@
         <v>374</v>
       </c>
       <c r="AF55" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG55" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AH55" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AI55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
         <v>1</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN55" t="n">
         <v>0</v>
@@ -9351,7 +9339,7 @@
         <v>374</v>
       </c>
       <c r="AR55" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AS55" t="n">
         <v>279</v>
@@ -9443,19 +9431,19 @@
         <v>37</v>
       </c>
       <c r="U56" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="V56" t="n">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="W56" t="n">
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Y56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -9467,31 +9455,31 @@
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AD56" t="n">
         <v>1</v>
       </c>
       <c r="AE56" t="n">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="AF56" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="AG56" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="AH56" t="n">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AK56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9503,16 +9491,16 @@
         <v>0</v>
       </c>
       <c r="AO56" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AP56" t="n">
         <v>1</v>
       </c>
       <c r="AQ56" t="n">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="AR56" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="AS56" t="n">
         <v>420</v>
@@ -9604,16 +9592,16 @@
         <v>68</v>
       </c>
       <c r="U57" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="V57" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="W57" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y57" t="n">
         <v>1</v>
@@ -9628,28 +9616,28 @@
         <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AF57" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AG57" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AH57" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AI57" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AJ57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK57" t="n">
         <v>1</v>
@@ -9664,16 +9652,16 @@
         <v>0</v>
       </c>
       <c r="AO57" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP57" t="n">
         <v>0</v>
       </c>
       <c r="AQ57" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AR57" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AS57" t="n">
         <v>336</v>
@@ -9765,22 +9753,22 @@
         <v>37</v>
       </c>
       <c r="U58" t="n">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="V58" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="W58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="X58" t="n">
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -9789,34 +9777,34 @@
         <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AD58" t="n">
         <v>2</v>
       </c>
       <c r="AE58" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AF58" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AG58" t="n">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="AH58" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AI58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AJ58" t="n">
         <v>0</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM58" t="n">
         <v>0</v>
@@ -9825,16 +9813,16 @@
         <v>0</v>
       </c>
       <c r="AO58" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AP58" t="n">
         <v>2</v>
       </c>
       <c r="AQ58" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AR58" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AS58" t="n">
         <v>363</v>
@@ -9926,16 +9914,16 @@
         <v>35</v>
       </c>
       <c r="U59" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="V59" t="n">
         <v>153</v>
       </c>
       <c r="W59" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="X59" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Y59" t="n">
         <v>0</v>
@@ -9956,22 +9944,22 @@
         <v>4</v>
       </c>
       <c r="AE59" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AF59" t="n">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="AG59" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="AH59" t="n">
         <v>153</v>
       </c>
       <c r="AI59" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AJ59" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AK59" t="n">
         <v>0</v>
@@ -9992,10 +9980,10 @@
         <v>4</v>
       </c>
       <c r="AQ59" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AR59" t="n">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="AS59" t="n">
         <v>383</v>
@@ -10087,76 +10075,76 @@
         <v>48</v>
       </c>
       <c r="U60" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="V60" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="W60" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="X60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y60" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="Z60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AF60" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AG60" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="AH60" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AI60" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK60" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AL60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AM60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN60" t="n">
         <v>0</v>
       </c>
       <c r="AO60" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AP60" t="n">
         <v>0</v>
       </c>
       <c r="AQ60" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AR60" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AS60" t="n">
         <v>377</v>
@@ -10409,22 +10397,22 @@
         <v>43</v>
       </c>
       <c r="U62" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="V62" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="W62" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
         <v>1</v>
       </c>
       <c r="Y62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -10439,28 +10427,28 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="AF62" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="AG62" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AH62" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="AI62" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="n">
         <v>1</v>
       </c>
       <c r="AK62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM62" t="n">
         <v>0</v>
@@ -10475,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AQ62" t="n">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="AR62" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="AS62" t="n">
         <v>365</v>
@@ -10570,13 +10558,13 @@
         <v>54</v>
       </c>
       <c r="U63" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="V63" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="W63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
@@ -10600,19 +10588,19 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AF63" t="n">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="AG63" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="AH63" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="AI63" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AJ63" t="n">
         <v>0</v>
@@ -10636,10 +10624,10 @@
         <v>0</v>
       </c>
       <c r="AQ63" t="n">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AR63" t="n">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="AS63" t="n">
         <v>324</v>
@@ -10731,19 +10719,19 @@
         <v>111</v>
       </c>
       <c r="U64" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="V64" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X64" t="n">
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -10761,16 +10749,16 @@
         <v>2</v>
       </c>
       <c r="AE64" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="AF64" t="n">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="AG64" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AH64" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -10779,7 +10767,7 @@
         <v>0</v>
       </c>
       <c r="AK64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL64" t="n">
         <v>0</v>
@@ -10797,10 +10785,10 @@
         <v>2</v>
       </c>
       <c r="AQ64" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AR64" t="n">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="AS64" t="n">
         <v>440</v>
@@ -10892,19 +10880,19 @@
         <v>16</v>
       </c>
       <c r="U65" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="V65" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="W65" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z65" t="n">
         <v>0</v>
@@ -10922,25 +10910,25 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AF65" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG65" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AH65" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="AI65" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="AJ65" t="n">
         <v>0</v>
       </c>
       <c r="AK65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10958,10 +10946,10 @@
         <v>0</v>
       </c>
       <c r="AQ65" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AR65" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AS65" t="n">
         <v>417</v>
@@ -11053,19 +11041,19 @@
         <v>32</v>
       </c>
       <c r="U66" t="n">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="V66" t="n">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="W66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X66" t="n">
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
@@ -11080,28 +11068,28 @@
         <v>21</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE66" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AF66" t="n">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="AG66" t="n">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="AH66" t="n">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="AI66" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AJ66" t="n">
         <v>0</v>
       </c>
       <c r="AK66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AL66" t="n">
         <v>0</v>
@@ -11119,10 +11107,10 @@
         <v>1</v>
       </c>
       <c r="AQ66" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AR66" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="AS66" t="n">
         <v>384</v>
@@ -11214,19 +11202,19 @@
         <v>11</v>
       </c>
       <c r="U67" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="V67" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="W67" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="X67" t="n">
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -11244,25 +11232,25 @@
         <v>5</v>
       </c>
       <c r="AE67" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AF67" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="AG67" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="AH67" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="AI67" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AJ67" t="n">
         <v>0</v>
       </c>
       <c r="AK67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AL67" t="n">
         <v>0</v>
@@ -11280,10 +11268,10 @@
         <v>5</v>
       </c>
       <c r="AQ67" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AR67" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="AS67" t="n">
         <v>297</v>
@@ -11375,19 +11363,19 @@
         <v>83</v>
       </c>
       <c r="U68" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="V68" t="n">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="W68" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="X68" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z68" t="n">
         <v>0</v>
@@ -11399,31 +11387,31 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="AF68" t="n">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="AG68" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="AH68" t="n">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="AI68" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="AJ68" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AK68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL68" t="n">
         <v>0</v>
@@ -11435,16 +11423,16 @@
         <v>0</v>
       </c>
       <c r="AO68" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AP68" t="n">
         <v>0</v>
       </c>
       <c r="AQ68" t="n">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="AR68" t="n">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="AS68" t="n">
         <v>395</v>
@@ -11536,19 +11524,19 @@
         <v>14</v>
       </c>
       <c r="U69" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="V69" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="W69" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="X69" t="n">
         <v>1</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z69" t="n">
         <v>0</v>
@@ -11560,31 +11548,31 @@
         <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AF69" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AG69" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AH69" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AI69" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AJ69" t="n">
         <v>1</v>
       </c>
       <c r="AK69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL69" t="n">
         <v>0</v>
@@ -11596,16 +11584,16 @@
         <v>0</v>
       </c>
       <c r="AO69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP69" t="n">
         <v>0</v>
       </c>
       <c r="AQ69" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AR69" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AS69" t="n">
         <v>317</v>
@@ -11697,19 +11685,19 @@
         <v>23</v>
       </c>
       <c r="U70" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="V70" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X70" t="n">
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -11730,22 +11718,22 @@
         <v>346</v>
       </c>
       <c r="AF70" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG70" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AH70" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AI70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ70" t="n">
         <v>0</v>
       </c>
       <c r="AK70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL70" t="n">
         <v>0</v>
@@ -11766,7 +11754,7 @@
         <v>346</v>
       </c>
       <c r="AR70" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AS70" t="n">
         <v>306</v>
@@ -11858,16 +11846,16 @@
         <v>74</v>
       </c>
       <c r="U71" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="V71" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="W71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X71" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="Y71" t="n">
         <v>0</v>
@@ -11888,22 +11876,22 @@
         <v>1</v>
       </c>
       <c r="AE71" t="n">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="AF71" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="AG71" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="AH71" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="AI71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AJ71" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="AK71" t="n">
         <v>0</v>
@@ -11924,10 +11912,10 @@
         <v>1</v>
       </c>
       <c r="AQ71" t="n">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="AR71" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="AS71" t="n">
         <v>366</v>
@@ -12019,16 +12007,16 @@
         <v>47</v>
       </c>
       <c r="U72" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="V72" t="n">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="W72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y72" t="n">
         <v>0</v>
@@ -12049,22 +12037,22 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="AF72" t="n">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="AG72" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="AH72" t="n">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="AI72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK72" t="n">
         <v>0</v>
@@ -12085,10 +12073,10 @@
         <v>0</v>
       </c>
       <c r="AQ72" t="n">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="AR72" t="n">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="AS72" t="n">
         <v>353</v>
@@ -12180,10 +12168,10 @@
         <v>17</v>
       </c>
       <c r="U73" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="V73" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="W73" t="n">
         <v>0</v>
@@ -12204,22 +12192,22 @@
         <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AD73" t="n">
         <v>1</v>
       </c>
       <c r="AE73" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AF73" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AG73" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AH73" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -12240,16 +12228,16 @@
         <v>0</v>
       </c>
       <c r="AO73" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AP73" t="n">
         <v>1</v>
       </c>
       <c r="AQ73" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AR73" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AS73" t="n">
         <v>362</v>
@@ -12341,16 +12329,16 @@
         <v>94</v>
       </c>
       <c r="U74" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="V74" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="W74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="Y74" t="n">
         <v>0</v>
@@ -12365,28 +12353,28 @@
         <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD74" t="n">
         <v>1</v>
       </c>
       <c r="AE74" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AF74" t="n">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AG74" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH74" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="AI74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ74" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="AK74" t="n">
         <v>0</v>
@@ -12401,16 +12389,16 @@
         <v>0</v>
       </c>
       <c r="AO74" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AP74" t="n">
         <v>1</v>
       </c>
       <c r="AQ74" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AR74" t="n">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AS74" t="n">
         <v>398</v>
@@ -12502,55 +12490,55 @@
         <v>40</v>
       </c>
       <c r="U75" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="V75" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="W75" t="n">
+        <v>5</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>413</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>251</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>161</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>214</v>
+      </c>
+      <c r="AI75" t="n">
         <v>4</v>
       </c>
-      <c r="X75" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>411</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>245</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>164</v>
-      </c>
-      <c r="AH75" t="n">
-        <v>202</v>
-      </c>
-      <c r="AI75" t="n">
-        <v>3</v>
-      </c>
       <c r="AJ75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK75" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AL75" t="n">
         <v>0</v>
@@ -12562,16 +12550,16 @@
         <v>0</v>
       </c>
       <c r="AO75" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AP75" t="n">
         <v>0</v>
       </c>
       <c r="AQ75" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AR75" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AS75" t="n">
         <v>359</v>
@@ -12663,13 +12651,13 @@
         <v>5</v>
       </c>
       <c r="U76" t="n">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="V76" t="n">
         <v>133</v>
       </c>
       <c r="W76" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="X76" t="n">
         <v>0</v>
@@ -12693,19 +12681,19 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AF76" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="AG76" t="n">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="AH76" t="n">
         <v>133</v>
       </c>
       <c r="AI76" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="AJ76" t="n">
         <v>0</v>
@@ -12729,10 +12717,10 @@
         <v>0</v>
       </c>
       <c r="AQ76" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AR76" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="AS76" t="n">
         <v>357</v>
@@ -12824,19 +12812,19 @@
         <v>32</v>
       </c>
       <c r="U77" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="V77" t="n">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="W77" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z77" t="n">
         <v>0</v>
@@ -12848,31 +12836,31 @@
         <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AF77" t="n">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="AG77" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="AH77" t="n">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="AI77" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AJ77" t="n">
         <v>9</v>
       </c>
       <c r="AK77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL77" t="n">
         <v>0</v>
@@ -12884,16 +12872,16 @@
         <v>0</v>
       </c>
       <c r="AO77" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="AP77" t="n">
         <v>0</v>
       </c>
       <c r="AQ77" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AR77" t="n">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="AS77" t="n">
         <v>386</v>
@@ -12985,19 +12973,19 @@
         <v>9</v>
       </c>
       <c r="U78" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="V78" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="W78" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="X78" t="n">
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z78" t="n">
         <v>0</v>
@@ -13009,31 +12997,31 @@
         <v>0</v>
       </c>
       <c r="AC78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD78" t="n">
         <v>1</v>
       </c>
       <c r="AE78" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="AF78" t="n">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="AG78" t="n">
         <v>150</v>
       </c>
       <c r="AH78" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AI78" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AJ78" t="n">
         <v>0</v>
       </c>
       <c r="AK78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL78" t="n">
         <v>0</v>
@@ -13045,16 +13033,16 @@
         <v>0</v>
       </c>
       <c r="AO78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP78" t="n">
         <v>1</v>
       </c>
       <c r="AQ78" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AR78" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AS78" t="n">
         <v>350</v>
@@ -13146,13 +13134,13 @@
         <v>70</v>
       </c>
       <c r="U79" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="V79" t="n">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="W79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X79" t="n">
         <v>0</v>
@@ -13176,19 +13164,19 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AF79" t="n">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="AG79" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AH79" t="n">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="AI79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ79" t="n">
         <v>0</v>
@@ -13212,10 +13200,10 @@
         <v>0</v>
       </c>
       <c r="AQ79" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AR79" t="n">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="AS79" t="n">
         <v>319</v>
@@ -13310,7 +13298,7 @@
         <v>96</v>
       </c>
       <c r="V80" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="W80" t="n">
         <v>0</v>
@@ -13319,7 +13307,7 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z80" t="n">
         <v>0</v>
@@ -13346,7 +13334,7 @@
         <v>96</v>
       </c>
       <c r="AH80" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -13355,7 +13343,7 @@
         <v>0</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL80" t="n">
         <v>0</v>
@@ -13629,19 +13617,19 @@
         <v>81</v>
       </c>
       <c r="U82" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="V82" t="n">
         <v>218</v>
       </c>
       <c r="W82" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X82" t="n">
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z82" t="n">
         <v>0</v>
@@ -13659,25 +13647,25 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AF82" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="AG82" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="AH82" t="n">
         <v>218</v>
       </c>
       <c r="AI82" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AJ82" t="n">
         <v>0</v>
       </c>
       <c r="AK82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL82" t="n">
         <v>0</v>
@@ -13695,10 +13683,10 @@
         <v>0</v>
       </c>
       <c r="AQ82" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AR82" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="AS82" t="n">
         <v>385</v>
@@ -13790,19 +13778,19 @@
         <v>26</v>
       </c>
       <c r="U83" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="V83" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="W83" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="X83" t="n">
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z83" t="n">
         <v>0</v>
@@ -13820,25 +13808,25 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AF83" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AG83" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AH83" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="AI83" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AJ83" t="n">
         <v>0</v>
       </c>
       <c r="AK83" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AL83" t="n">
         <v>0</v>
@@ -13856,10 +13844,10 @@
         <v>0</v>
       </c>
       <c r="AQ83" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AR83" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AS83" t="n">
         <v>340</v>
@@ -13951,16 +13939,16 @@
         <v>18</v>
       </c>
       <c r="U84" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="V84" t="n">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="W84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="Y84" t="n">
         <v>0</v>
@@ -13975,28 +13963,28 @@
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AF84" t="n">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="AG84" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="AH84" t="n">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
       </c>
       <c r="AJ84" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AK84" t="n">
         <v>0</v>
@@ -14011,16 +13999,16 @@
         <v>0</v>
       </c>
       <c r="AO84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AP84" t="n">
         <v>0</v>
       </c>
       <c r="AQ84" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AR84" t="n">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="AS84" t="n">
         <v>378</v>
@@ -14112,13 +14100,13 @@
         <v>73</v>
       </c>
       <c r="U85" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="V85" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="W85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="X85" t="n">
         <v>0</v>
@@ -14136,25 +14124,25 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AD85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AF85" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AG85" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="AH85" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AI85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ85" t="n">
         <v>0</v>
@@ -14172,16 +14160,16 @@
         <v>0</v>
       </c>
       <c r="AO85" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AP85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ85" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AR85" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AS85" t="n">
         <v>367</v>
@@ -14273,22 +14261,22 @@
         <v>39</v>
       </c>
       <c r="U86" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V86" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="W86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X86" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y86" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="Z86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -14297,7 +14285,7 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -14306,25 +14294,25 @@
         <v>447</v>
       </c>
       <c r="AF86" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AG86" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AH86" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="AI86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ86" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AK86" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AL86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM86" t="n">
         <v>0</v>
@@ -14333,7 +14321,7 @@
         <v>0</v>
       </c>
       <c r="AO86" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AP86" t="n">
         <v>0</v>
@@ -14342,7 +14330,7 @@
         <v>447</v>
       </c>
       <c r="AR86" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AS86" t="n">
         <v>367</v>
@@ -14434,16 +14422,16 @@
         <v>16</v>
       </c>
       <c r="U87" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="V87" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="W87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X87" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Y87" t="n">
         <v>27</v>
@@ -14458,28 +14446,28 @@
         <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AF87" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AG87" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AH87" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AI87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ87" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AK87" t="n">
         <v>27</v>
@@ -14494,16 +14482,16 @@
         <v>0</v>
       </c>
       <c r="AO87" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP87" t="n">
         <v>0</v>
       </c>
       <c r="AQ87" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AR87" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AS87" t="n">
         <v>360</v>
@@ -14595,16 +14583,16 @@
         <v>39</v>
       </c>
       <c r="U88" t="n">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="V88" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="W88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X88" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="Y88" t="n">
         <v>1</v>
@@ -14619,28 +14607,28 @@
         <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AD88" t="n">
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="AF88" t="n">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="AG88" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="AH88" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AI88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ88" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AK88" t="n">
         <v>1</v>
@@ -14655,16 +14643,16 @@
         <v>0</v>
       </c>
       <c r="AO88" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AP88" t="n">
         <v>0</v>
       </c>
       <c r="AQ88" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AR88" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="AS88" t="n">
         <v>356</v>
@@ -14756,19 +14744,19 @@
         <v>38</v>
       </c>
       <c r="U89" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="V89" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="W89" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="X89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z89" t="n">
         <v>0</v>
@@ -14780,7 +14768,7 @@
         <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="AD89" t="n">
         <v>0</v>
@@ -14789,22 +14777,22 @@
         <v>492</v>
       </c>
       <c r="AF89" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AG89" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AH89" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AI89" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="AJ89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AK89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL89" t="n">
         <v>0</v>
@@ -14816,7 +14804,7 @@
         <v>0</v>
       </c>
       <c r="AO89" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="AP89" t="n">
         <v>0</v>
@@ -14825,7 +14813,7 @@
         <v>492</v>
       </c>
       <c r="AR89" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AS89" t="n">
         <v>405</v>
@@ -14917,16 +14905,16 @@
         <v>16</v>
       </c>
       <c r="U90" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="V90" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="W90" t="n">
         <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="Y90" t="n">
         <v>0</v>
@@ -14941,28 +14929,28 @@
         <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE90" t="n">
         <v>323</v>
       </c>
       <c r="AF90" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AG90" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="AH90" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
       </c>
       <c r="AJ90" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="AK90" t="n">
         <v>0</v>
@@ -14977,16 +14965,16 @@
         <v>0</v>
       </c>
       <c r="AO90" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ90" t="n">
         <v>323</v>
       </c>
       <c r="AR90" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AS90" t="n">
         <v>301</v>
@@ -15078,13 +15066,13 @@
         <v>26</v>
       </c>
       <c r="U91" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="V91" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="W91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="X91" t="n">
         <v>0</v>
@@ -15108,19 +15096,19 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AF91" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="AG91" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="AH91" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="AI91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AJ91" t="n">
         <v>0</v>
@@ -15144,10 +15132,10 @@
         <v>0</v>
       </c>
       <c r="AQ91" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AR91" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="AS91" t="n">
         <v>399</v>
@@ -15239,13 +15227,13 @@
         <v>48</v>
       </c>
       <c r="U92" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="V92" t="n">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="W92" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
         <v>5</v>
@@ -15269,19 +15257,19 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AF92" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AG92" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AH92" t="n">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="AI92" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="AJ92" t="n">
         <v>5</v>
@@ -15305,10 +15293,10 @@
         <v>0</v>
       </c>
       <c r="AQ92" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AR92" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AS92" t="n">
         <v>364</v>
@@ -15400,10 +15388,10 @@
         <v>22</v>
       </c>
       <c r="U93" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="V93" t="n">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="W93" t="n">
         <v>0</v>
@@ -15412,7 +15400,7 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
         <v>0</v>
@@ -15430,16 +15418,16 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AF93" t="n">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="AG93" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="AH93" t="n">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -15448,7 +15436,7 @@
         <v>0</v>
       </c>
       <c r="AK93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL93" t="n">
         <v>0</v>
@@ -15466,10 +15454,10 @@
         <v>0</v>
       </c>
       <c r="AQ93" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AR93" t="n">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="AS93" t="n">
         <v>335</v>
@@ -15564,16 +15552,16 @@
         <v>198</v>
       </c>
       <c r="V94" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="W94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
         <v>0</v>
@@ -15585,7 +15573,7 @@
         <v>1</v>
       </c>
       <c r="AC94" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="AD94" t="n">
         <v>0</v>
@@ -15594,22 +15582,22 @@
         <v>408</v>
       </c>
       <c r="AF94" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG94" t="n">
         <v>198</v>
       </c>
       <c r="AH94" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="AI94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL94" t="n">
         <v>0</v>
@@ -15621,7 +15609,7 @@
         <v>1</v>
       </c>
       <c r="AO94" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="AP94" t="n">
         <v>0</v>
@@ -15630,7 +15618,7 @@
         <v>408</v>
       </c>
       <c r="AR94" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AS94" t="n">
         <v>373</v>
@@ -15722,19 +15710,19 @@
         <v>10</v>
       </c>
       <c r="U95" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="V95" t="n">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="W95" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="X95" t="n">
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z95" t="n">
         <v>0</v>
@@ -15752,25 +15740,25 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AF95" t="n">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="AG95" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="AH95" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AI95" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AJ95" t="n">
         <v>0</v>
       </c>
       <c r="AK95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL95" t="n">
         <v>0</v>
@@ -15788,10 +15776,10 @@
         <v>0</v>
       </c>
       <c r="AQ95" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AR95" t="n">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="AS95" t="n">
         <v>356</v>
@@ -15883,19 +15871,19 @@
         <v>42</v>
       </c>
       <c r="U96" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="V96" t="n">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="W96" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="X96" t="n">
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -15913,25 +15901,25 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AF96" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="AG96" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="AH96" t="n">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="AI96" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="AJ96" t="n">
         <v>0</v>
       </c>
       <c r="AK96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL96" t="n">
         <v>0</v>
@@ -15949,10 +15937,10 @@
         <v>0</v>
       </c>
       <c r="AQ96" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AR96" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="AS96" t="n">
         <v>282</v>
@@ -16044,49 +16032,49 @@
         <v>55</v>
       </c>
       <c r="U97" t="n">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="V97" t="n">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="W97" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="X97" t="n">
         <v>44</v>
       </c>
       <c r="Y97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB97" t="n">
         <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE97" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AF97" t="n">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="AG97" t="n">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="AH97" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="AI97" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AJ97" t="n">
         <v>44</v>
@@ -16098,22 +16086,22 @@
         <v>0</v>
       </c>
       <c r="AM97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN97" t="n">
         <v>0</v>
       </c>
       <c r="AO97" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AP97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ97" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AR97" t="n">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="AS97" t="n">
         <v>378</v>
@@ -16205,19 +16193,19 @@
         <v>4</v>
       </c>
       <c r="U98" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="V98" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="W98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="X98" t="n">
         <v>9</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -16238,22 +16226,22 @@
         <v>399</v>
       </c>
       <c r="AF98" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG98" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AH98" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="AI98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AJ98" t="n">
         <v>9</v>
       </c>
       <c r="AK98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL98" t="n">
         <v>0</v>
@@ -16274,7 +16262,7 @@
         <v>399</v>
       </c>
       <c r="AR98" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AS98" t="n">
         <v>367</v>
@@ -16366,10 +16354,10 @@
         <v>63</v>
       </c>
       <c r="U99" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="V99" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="W99" t="n">
         <v>0</v>
@@ -16378,7 +16366,7 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -16396,16 +16384,16 @@
         <v>2</v>
       </c>
       <c r="AE99" t="n">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="AF99" t="n">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="AG99" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="AH99" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="AI99" t="n">
         <v>0</v>
@@ -16414,7 +16402,7 @@
         <v>0</v>
       </c>
       <c r="AK99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AL99" t="n">
         <v>0</v>
@@ -16432,10 +16420,10 @@
         <v>2</v>
       </c>
       <c r="AQ99" t="n">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="AR99" t="n">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="AS99" t="n">
         <v>321</v>
@@ -16527,19 +16515,19 @@
         <v>41</v>
       </c>
       <c r="U100" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="V100" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="W100" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="X100" t="n">
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -16551,31 +16539,31 @@
         <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AF100" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="AG100" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="AH100" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="AI100" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AJ100" t="n">
         <v>0</v>
       </c>
       <c r="AK100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL100" t="n">
         <v>0</v>
@@ -16587,16 +16575,16 @@
         <v>0</v>
       </c>
       <c r="AO100" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AP100" t="n">
         <v>0</v>
       </c>
       <c r="AQ100" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AR100" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="AS100" t="n">
         <v>343</v>
@@ -16688,58 +16676,58 @@
         <v>47</v>
       </c>
       <c r="U101" t="n">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="V101" t="n">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="W101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X101" t="n">
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>84</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>509</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>311</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>199</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>219</v>
+      </c>
+      <c r="AI101" t="n">
         <v>2</v>
       </c>
-      <c r="AA101" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC101" t="n">
-        <v>82</v>
-      </c>
-      <c r="AD101" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE101" t="n">
-        <v>502</v>
-      </c>
-      <c r="AF101" t="n">
-        <v>290</v>
-      </c>
-      <c r="AG101" t="n">
-        <v>212</v>
-      </c>
-      <c r="AH101" t="n">
-        <v>203</v>
-      </c>
-      <c r="AI101" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ101" t="n">
         <v>0</v>
       </c>
       <c r="AK101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM101" t="n">
         <v>1</v>
@@ -16748,16 +16736,16 @@
         <v>0</v>
       </c>
       <c r="AO101" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AP101" t="n">
         <v>1</v>
       </c>
       <c r="AQ101" t="n">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="AR101" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AS101" t="n">
         <v>455</v>
@@ -16849,13 +16837,13 @@
         <v>35</v>
       </c>
       <c r="U102" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="V102" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="W102" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="X102" t="n">
         <v>5</v>
@@ -16879,19 +16867,19 @@
         <v>2</v>
       </c>
       <c r="AE102" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AF102" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AG102" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="AH102" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AI102" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AJ102" t="n">
         <v>5</v>
@@ -16915,10 +16903,10 @@
         <v>2</v>
       </c>
       <c r="AQ102" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AR102" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AS102" t="n">
         <v>472</v>
@@ -17010,10 +16998,10 @@
         <v>33</v>
       </c>
       <c r="U103" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="V103" t="n">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="W103" t="n">
         <v>0</v>
@@ -17022,7 +17010,7 @@
         <v>1</v>
       </c>
       <c r="Y103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -17040,25 +17028,25 @@
         <v>1</v>
       </c>
       <c r="AE103" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AF103" t="n">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="AG103" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="AH103" t="n">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="AI103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ103" t="n">
         <v>1</v>
       </c>
       <c r="AK103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AL103" t="n">
         <v>0</v>
@@ -17076,10 +17064,10 @@
         <v>1</v>
       </c>
       <c r="AQ103" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AR103" t="n">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="AS103" t="n">
         <v>316</v>
@@ -17171,19 +17159,19 @@
         <v>14</v>
       </c>
       <c r="U104" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V104" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="W104" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="X104" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Y104" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z104" t="n">
         <v>0</v>
@@ -17201,25 +17189,25 @@
         <v>3</v>
       </c>
       <c r="AE104" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AF104" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="AG104" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AH104" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AI104" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AJ104" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AK104" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AL104" t="n">
         <v>0</v>
@@ -17237,10 +17225,10 @@
         <v>3</v>
       </c>
       <c r="AQ104" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AR104" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="AS104" t="n">
         <v>422</v>
@@ -17332,16 +17320,16 @@
         <v>56</v>
       </c>
       <c r="U105" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="V105" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="W105" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="X105" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Y105" t="n">
         <v>0</v>
@@ -17362,22 +17350,22 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AF105" t="n">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="AG105" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="AH105" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AI105" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="AJ105" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AK105" t="n">
         <v>0</v>
@@ -17398,10 +17386,10 @@
         <v>0</v>
       </c>
       <c r="AQ105" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AR105" t="n">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="AS105" t="n">
         <v>391</v>
@@ -17493,10 +17481,10 @@
         <v>43</v>
       </c>
       <c r="U106" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="V106" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="W106" t="n">
         <v>0</v>
@@ -17505,7 +17493,7 @@
         <v>1</v>
       </c>
       <c r="Y106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -17517,22 +17505,22 @@
         <v>0</v>
       </c>
       <c r="AC106" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AD106" t="n">
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="AF106" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="AG106" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="AH106" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="AI106" t="n">
         <v>0</v>
@@ -17541,7 +17529,7 @@
         <v>1</v>
       </c>
       <c r="AK106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AL106" t="n">
         <v>0</v>
@@ -17553,16 +17541,16 @@
         <v>0</v>
       </c>
       <c r="AO106" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AP106" t="n">
         <v>0</v>
       </c>
       <c r="AQ106" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="AR106" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="AS106" t="n">
         <v>366</v>
@@ -17654,13 +17642,13 @@
         <v>33</v>
       </c>
       <c r="U107" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="V107" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="W107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X107" t="n">
         <v>0</v>
@@ -17687,16 +17675,16 @@
         <v>367</v>
       </c>
       <c r="AF107" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="AG107" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="AH107" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="AI107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AJ107" t="n">
         <v>0</v>
@@ -17723,7 +17711,7 @@
         <v>367</v>
       </c>
       <c r="AR107" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="AS107" t="n">
         <v>322</v>
@@ -17815,19 +17803,19 @@
         <v>20</v>
       </c>
       <c r="U108" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="V108" t="n">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="W108" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="X108" t="n">
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z108" t="n">
         <v>0</v>
@@ -17848,22 +17836,22 @@
         <v>382</v>
       </c>
       <c r="AF108" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="AG108" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="AH108" t="n">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="AI108" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ108" t="n">
         <v>0</v>
       </c>
       <c r="AK108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL108" t="n">
         <v>0</v>
@@ -17884,7 +17872,7 @@
         <v>382</v>
       </c>
       <c r="AR108" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="AS108" t="n">
         <v>324</v>
@@ -17976,19 +17964,19 @@
         <v>14</v>
       </c>
       <c r="U109" t="n">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="V109" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="W109" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="X109" t="n">
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
         <v>0</v>
@@ -18000,31 +17988,31 @@
         <v>0</v>
       </c>
       <c r="AC109" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AD109" t="n">
         <v>1</v>
       </c>
       <c r="AE109" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="AF109" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="AG109" t="n">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AH109" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AI109" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AJ109" t="n">
         <v>0</v>
       </c>
       <c r="AK109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL109" t="n">
         <v>0</v>
@@ -18036,16 +18024,16 @@
         <v>0</v>
       </c>
       <c r="AO109" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AP109" t="n">
         <v>1</v>
       </c>
       <c r="AQ109" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="AR109" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="AS109" t="n">
         <v>407</v>
@@ -18137,19 +18125,19 @@
         <v>145</v>
       </c>
       <c r="U110" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="V110" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="W110" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="X110" t="n">
         <v>5</v>
       </c>
       <c r="Y110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z110" t="n">
         <v>0</v>
@@ -18164,28 +18152,28 @@
         <v>20</v>
       </c>
       <c r="AD110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE110" t="n">
         <v>622</v>
       </c>
       <c r="AF110" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AG110" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="AH110" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="AI110" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AJ110" t="n">
         <v>5</v>
       </c>
       <c r="AK110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL110" t="n">
         <v>0</v>
@@ -18200,13 +18188,13 @@
         <v>20</v>
       </c>
       <c r="AP110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ110" t="n">
         <v>622</v>
       </c>
       <c r="AR110" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AS110" t="n">
         <v>507</v>
@@ -18298,13 +18286,13 @@
         <v>34</v>
       </c>
       <c r="U111" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="V111" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="W111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X111" t="n">
         <v>2</v>
@@ -18328,19 +18316,19 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AF111" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="AG111" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AH111" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="AI111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ111" t="n">
         <v>2</v>
@@ -18364,10 +18352,10 @@
         <v>0</v>
       </c>
       <c r="AQ111" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AR111" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="AS111" t="n">
         <v>294</v>
@@ -18459,10 +18447,10 @@
         <v>14</v>
       </c>
       <c r="U112" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="V112" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="W112" t="n">
         <v>0</v>
@@ -18483,22 +18471,22 @@
         <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="AF112" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="AG112" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AH112" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
@@ -18519,16 +18507,16 @@
         <v>0</v>
       </c>
       <c r="AO112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AP112" t="n">
         <v>0</v>
       </c>
       <c r="AQ112" t="n">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="AR112" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="AS112" t="n">
         <v>403</v>
@@ -18620,19 +18608,19 @@
         <v>25</v>
       </c>
       <c r="U113" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="V113" t="n">
-        <v>194</v>
+        <v>278</v>
       </c>
       <c r="W113" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="X113" t="n">
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="Z113" t="n">
         <v>0</v>
@@ -18644,31 +18632,31 @@
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="AF113" t="n">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="AG113" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="AH113" t="n">
-        <v>194</v>
+        <v>278</v>
       </c>
       <c r="AI113" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="AJ113" t="n">
         <v>0</v>
       </c>
       <c r="AK113" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AL113" t="n">
         <v>0</v>
@@ -18680,16 +18668,16 @@
         <v>0</v>
       </c>
       <c r="AO113" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AP113" t="n">
         <v>0</v>
       </c>
       <c r="AQ113" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="AR113" t="n">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="AS113" t="n">
         <v>362</v>
@@ -18784,10 +18772,10 @@
         <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="W114" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="X114" t="n">
         <v>0</v>
@@ -18805,7 +18793,7 @@
         <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AD114" t="n">
         <v>4</v>
@@ -18820,10 +18808,10 @@
         <v>0</v>
       </c>
       <c r="AH114" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="AI114" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AJ114" t="n">
         <v>0</v>
@@ -18841,7 +18829,7 @@
         <v>0</v>
       </c>
       <c r="AO114" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AP114" t="n">
         <v>4</v>
@@ -18945,7 +18933,7 @@
         <v>212</v>
       </c>
       <c r="V115" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="W115" t="n">
         <v>6</v>
@@ -18966,7 +18954,7 @@
         <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -18981,7 +18969,7 @@
         <v>212</v>
       </c>
       <c r="AH115" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AI115" t="n">
         <v>6</v>
@@ -19002,7 +18990,7 @@
         <v>0</v>
       </c>
       <c r="AO115" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AP115" t="n">
         <v>0</v>
@@ -19103,13 +19091,13 @@
         <v>28</v>
       </c>
       <c r="U116" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="V116" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="W116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X116" t="n">
         <v>0</v>
@@ -19133,19 +19121,19 @@
         <v>1</v>
       </c>
       <c r="AE116" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AF116" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AG116" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="AH116" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="AI116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ116" t="n">
         <v>0</v>
@@ -19169,10 +19157,10 @@
         <v>1</v>
       </c>
       <c r="AQ116" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AR116" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AS116" t="n">
         <v>333</v>
@@ -19264,19 +19252,19 @@
         <v>34</v>
       </c>
       <c r="U117" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="V117" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="W117" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="X117" t="n">
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z117" t="n">
         <v>0</v>
@@ -19288,31 +19276,31 @@
         <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AD117" t="n">
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AF117" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="AG117" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AH117" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="AI117" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AJ117" t="n">
         <v>0</v>
       </c>
       <c r="AK117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL117" t="n">
         <v>0</v>
@@ -19324,16 +19312,16 @@
         <v>0</v>
       </c>
       <c r="AO117" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AP117" t="n">
         <v>0</v>
       </c>
       <c r="AQ117" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AR117" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="AS117" t="n">
         <v>364</v>
@@ -19425,16 +19413,16 @@
         <v>73</v>
       </c>
       <c r="U118" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="V118" t="n">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="W118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y118" t="n">
         <v>0</v>
@@ -19455,22 +19443,22 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="AF118" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="AG118" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AH118" t="n">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="AI118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK118" t="n">
         <v>0</v>
@@ -19491,10 +19479,10 @@
         <v>0</v>
       </c>
       <c r="AQ118" t="n">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="AR118" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="AS118" t="n">
         <v>378</v>
@@ -19586,13 +19574,13 @@
         <v>65</v>
       </c>
       <c r="U119" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="V119" t="n">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="W119" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="X119" t="n">
         <v>0</v>
@@ -19616,19 +19604,19 @@
         <v>3</v>
       </c>
       <c r="AE119" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AF119" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="AG119" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AH119" t="n">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="AI119" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="AJ119" t="n">
         <v>0</v>
@@ -19652,10 +19640,10 @@
         <v>3</v>
       </c>
       <c r="AQ119" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AR119" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="AS119" t="n">
         <v>420</v>
@@ -19747,76 +19735,76 @@
         <v>80</v>
       </c>
       <c r="U120" t="n">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="V120" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="W120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X120" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA120" t="n">
         <v>3</v>
       </c>
-      <c r="Y120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z120" t="n">
+      <c r="AB120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>80</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>511</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>273</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>236</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>181</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ120" t="n">
         <v>2</v>
       </c>
-      <c r="AA120" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC120" t="n">
-        <v>56</v>
-      </c>
-      <c r="AD120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE120" t="n">
-        <v>509</v>
-      </c>
-      <c r="AF120" t="n">
-        <v>250</v>
-      </c>
-      <c r="AG120" t="n">
-        <v>254</v>
-      </c>
-      <c r="AH120" t="n">
-        <v>169</v>
-      </c>
-      <c r="AI120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ120" t="n">
+      <c r="AK120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM120" t="n">
         <v>3</v>
       </c>
-      <c r="AK120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL120" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM120" t="n">
-        <v>2</v>
-      </c>
       <c r="AN120" t="n">
         <v>0</v>
       </c>
       <c r="AO120" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AP120" t="n">
         <v>0</v>
       </c>
       <c r="AQ120" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AR120" t="n">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="AS120" t="n">
         <v>430</v>
@@ -19908,19 +19896,19 @@
         <v>37</v>
       </c>
       <c r="U121" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="V121" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="W121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X121" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
         <v>0</v>
@@ -19932,31 +19920,31 @@
         <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE121" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AF121" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AG121" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AH121" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="AI121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ121" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL121" t="n">
         <v>0</v>
@@ -19968,16 +19956,16 @@
         <v>0</v>
       </c>
       <c r="AO121" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AP121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ121" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AR121" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AS121" t="n">
         <v>379</v>
@@ -20069,10 +20057,10 @@
         <v>27</v>
       </c>
       <c r="U122" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="V122" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="W122" t="n">
         <v>2</v>
@@ -20081,7 +20069,7 @@
         <v>1</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z122" t="n">
         <v>0</v>
@@ -20099,16 +20087,16 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AF122" t="n">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="AG122" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="AH122" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="AI122" t="n">
         <v>2</v>
@@ -20117,7 +20105,7 @@
         <v>1</v>
       </c>
       <c r="AK122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL122" t="n">
         <v>0</v>
@@ -20135,10 +20123,10 @@
         <v>0</v>
       </c>
       <c r="AQ122" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AR122" t="n">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="AS122" t="n">
         <v>419</v>
@@ -20230,13 +20218,13 @@
         <v>32</v>
       </c>
       <c r="U123" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="V123" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="W123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X123" t="n">
         <v>5</v>
@@ -20245,7 +20233,7 @@
         <v>1</v>
       </c>
       <c r="Z123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -20263,16 +20251,16 @@
         <v>493</v>
       </c>
       <c r="AF123" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AG123" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="AH123" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="AI123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ123" t="n">
         <v>5</v>
@@ -20281,7 +20269,7 @@
         <v>1</v>
       </c>
       <c r="AL123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM123" t="n">
         <v>0</v>
@@ -20299,7 +20287,7 @@
         <v>493</v>
       </c>
       <c r="AR123" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AS123" t="n">
         <v>432</v>
@@ -20391,13 +20379,13 @@
         <v>91</v>
       </c>
       <c r="U124" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V124" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="W124" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X124" t="n">
         <v>4</v>
@@ -20421,19 +20409,19 @@
         <v>1</v>
       </c>
       <c r="AE124" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AF124" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG124" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="AH124" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AI124" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ124" t="n">
         <v>4</v>
@@ -20457,10 +20445,10 @@
         <v>1</v>
       </c>
       <c r="AQ124" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AR124" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="AS124" t="n">
         <v>437</v>
@@ -20552,19 +20540,19 @@
         <v>46</v>
       </c>
       <c r="U125" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="V125" t="n">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="W125" t="n">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="X125" t="n">
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z125" t="n">
         <v>0</v>
@@ -20582,25 +20570,25 @@
         <v>2</v>
       </c>
       <c r="AE125" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AF125" t="n">
-        <v>266</v>
+        <v>319</v>
       </c>
       <c r="AG125" t="n">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="AH125" t="n">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="AI125" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="AJ125" t="n">
         <v>0</v>
       </c>
       <c r="AK125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL125" t="n">
         <v>0</v>
@@ -20618,10 +20606,10 @@
         <v>2</v>
       </c>
       <c r="AQ125" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AR125" t="n">
-        <v>265</v>
+        <v>319</v>
       </c>
       <c r="AS125" t="n">
         <v>303</v>
@@ -20713,10 +20701,10 @@
         <v>26</v>
       </c>
       <c r="U126" t="n">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="V126" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="W126" t="n">
         <v>0</v>
@@ -20737,25 +20725,25 @@
         <v>0</v>
       </c>
       <c r="AC126" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AD126" t="n">
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AF126" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="AG126" t="n">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="AH126" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AI126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ126" t="n">
         <v>0</v>
@@ -20773,16 +20761,16 @@
         <v>0</v>
       </c>
       <c r="AO126" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AP126" t="n">
         <v>0</v>
       </c>
       <c r="AQ126" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AR126" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="AS126" t="n">
         <v>366</v>
@@ -20874,16 +20862,16 @@
         <v>62</v>
       </c>
       <c r="U127" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="V127" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="W127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X127" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y127" t="n">
         <v>2</v>
@@ -20904,22 +20892,22 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AF127" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AG127" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="AH127" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="AI127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ127" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AK127" t="n">
         <v>2</v>
@@ -20940,10 +20928,10 @@
         <v>0</v>
       </c>
       <c r="AQ127" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AR127" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AS127" t="n">
         <v>394</v>
@@ -21038,13 +21026,13 @@
         <v>180</v>
       </c>
       <c r="V128" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="W128" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="X128" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="Y128" t="n">
         <v>2</v>
@@ -21059,7 +21047,7 @@
         <v>0</v>
       </c>
       <c r="AC128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AD128" t="n">
         <v>0</v>
@@ -21068,19 +21056,19 @@
         <v>470</v>
       </c>
       <c r="AF128" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AG128" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AH128" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="AI128" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AJ128" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AK128" t="n">
         <v>2</v>
@@ -21095,7 +21083,7 @@
         <v>0</v>
       </c>
       <c r="AO128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AP128" t="n">
         <v>0</v>
@@ -21104,7 +21092,7 @@
         <v>470</v>
       </c>
       <c r="AR128" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AS128" t="n">
         <v>372</v>
@@ -21196,13 +21184,13 @@
         <v>42</v>
       </c>
       <c r="U129" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="V129" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="W129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X129" t="n">
         <v>0</v>
@@ -21229,16 +21217,16 @@
         <v>345</v>
       </c>
       <c r="AF129" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="AG129" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="AH129" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="AI129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ129" t="n">
         <v>0</v>
@@ -21265,7 +21253,7 @@
         <v>345</v>
       </c>
       <c r="AR129" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="AS129" t="n">
         <v>313</v>
@@ -21357,19 +21345,19 @@
         <v>8</v>
       </c>
       <c r="U130" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="V130" t="n">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="W130" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z130" t="n">
         <v>0</v>
@@ -21387,25 +21375,25 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AF130" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="AG130" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="AH130" t="n">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="AI130" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="AJ130" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AK130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL130" t="n">
         <v>0</v>
@@ -21423,10 +21411,10 @@
         <v>0</v>
       </c>
       <c r="AQ130" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AR130" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="AS130" t="n">
         <v>386</v>
@@ -21518,13 +21506,13 @@
         <v>38</v>
       </c>
       <c r="U131" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="V131" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="W131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X131" t="n">
         <v>1</v>
@@ -21542,7 +21530,7 @@
         <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -21551,16 +21539,16 @@
         <v>399</v>
       </c>
       <c r="AF131" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AG131" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AH131" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="AI131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ131" t="n">
         <v>1</v>
@@ -21578,7 +21566,7 @@
         <v>0</v>
       </c>
       <c r="AO131" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="AP131" t="n">
         <v>0</v>
@@ -21587,7 +21575,7 @@
         <v>399</v>
       </c>
       <c r="AR131" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AS131" t="n">
         <v>370</v>
@@ -21679,13 +21667,13 @@
         <v>52</v>
       </c>
       <c r="U132" t="n">
+        <v>182</v>
+      </c>
+      <c r="V132" t="n">
         <v>188</v>
       </c>
-      <c r="V132" t="n">
-        <v>189</v>
-      </c>
       <c r="W132" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="X132" t="n">
         <v>0</v>
@@ -21703,25 +21691,25 @@
         <v>0</v>
       </c>
       <c r="AC132" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AD132" t="n">
         <v>1</v>
       </c>
       <c r="AE132" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AF132" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AG132" t="n">
+        <v>182</v>
+      </c>
+      <c r="AH132" t="n">
         <v>188</v>
       </c>
-      <c r="AH132" t="n">
-        <v>189</v>
-      </c>
       <c r="AI132" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AJ132" t="n">
         <v>0</v>
@@ -21739,16 +21727,16 @@
         <v>0</v>
       </c>
       <c r="AO132" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AP132" t="n">
         <v>1</v>
       </c>
       <c r="AQ132" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AR132" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AS132" t="n">
         <v>368</v>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROPORSI PERTANIAN NON PERTANIA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROPORSI PERTANIAN NON PERTANIA.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,252 +429,252 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha SE2026</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Jumlah UTP Subsektor Target (ST2023)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Jumlah UTP Subsektor Prelist</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Pertanian</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Persentase Pertanian</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Non Pertanian</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>USAHA BARU - Pertanian​</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>USAHA BARU - Persentase Pertanian​</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>USAHA BARU - Non Pertanian​</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Pertanian​​</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Persentase Pertanian​​</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Non Pertanian​​</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Pertanian​​​</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Persentase Pertanian​​​</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Non Pertanian​​​</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROPORSI PERTANIAN NON PERTANIA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_PROPORSI PERTANIAN NON PERTANIA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,256 +413,256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX132"/>
+  <dimension ref="A1:AX133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Jumlah Prelist Usaha SE2026</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Jumlah UTP Subsektor Target (ST2023)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Jumlah UTP Subsektor Prelist</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Pertanian</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Persentase Pertanian</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>USAHA DITEMUKAN - Non Pertanian</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>USAHA BARU - Pertanian​</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>USAHA BARU - Persentase Pertanian​</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>USAHA BARU - Non Pertanian​</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Pertanian​​</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Persentase Pertanian​​</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA DITEMUKAN - Non Pertanian​​</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Pertanian​​​</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Persentase Pertanian​​​</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>USAHA DALAM KELUARGA BARU - Non Pertanian​​​</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>
@@ -829,19 +817,19 @@
         <v>447</v>
       </c>
       <c r="AT2" t="n">
-        <v>364</v>
+        <v>64</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>4</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3">
@@ -1157,7 +1145,7 @@
         <v>342</v>
       </c>
       <c r="AT4" t="n">
-        <v>363</v>
+        <v>94</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
@@ -1169,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5">
@@ -1321,7 +1309,7 @@
         <v>249</v>
       </c>
       <c r="AT5" t="n">
-        <v>384</v>
+        <v>184</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
@@ -1330,10 +1318,10 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6">
@@ -1485,7 +1473,7 @@
         <v>233</v>
       </c>
       <c r="AT6" t="n">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="AU6" t="n">
         <v>0</v>
@@ -1497,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
@@ -1649,19 +1637,19 @@
         <v>395</v>
       </c>
       <c r="AT7" t="n">
-        <v>336</v>
+        <v>27</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8">
@@ -1813,19 +1801,19 @@
         <v>285</v>
       </c>
       <c r="AT8" t="n">
-        <v>304</v>
+        <v>85</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AV8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9">
@@ -1977,19 +1965,19 @@
         <v>389</v>
       </c>
       <c r="AT9" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -2141,19 +2129,19 @@
         <v>278</v>
       </c>
       <c r="AT10" t="n">
-        <v>324</v>
+        <v>141</v>
       </c>
       <c r="AU10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -2305,19 +2293,19 @@
         <v>271</v>
       </c>
       <c r="AT11" t="n">
-        <v>373</v>
+        <v>142</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX11" t="n">
-        <v>2</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12">
@@ -2469,19 +2457,19 @@
         <v>386</v>
       </c>
       <c r="AT12" t="n">
-        <v>383</v>
+        <v>104</v>
       </c>
       <c r="AU12" t="n">
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -2633,19 +2621,19 @@
         <v>493</v>
       </c>
       <c r="AT13" t="n">
-        <v>373</v>
+        <v>75</v>
       </c>
       <c r="AU13" t="n">
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14">
@@ -2797,19 +2785,19 @@
         <v>347</v>
       </c>
       <c r="AT14" t="n">
-        <v>364</v>
+        <v>74</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AV14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>3</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15">
@@ -2961,19 +2949,19 @@
         <v>308</v>
       </c>
       <c r="AT15" t="n">
-        <v>324</v>
+        <v>156</v>
       </c>
       <c r="AU15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AW15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16">
@@ -3125,19 +3113,19 @@
         <v>382</v>
       </c>
       <c r="AT16" t="n">
-        <v>288</v>
+        <v>40</v>
       </c>
       <c r="AU16" t="n">
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17">
@@ -3178,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -3199,13 +3187,13 @@
         <v>14</v>
       </c>
       <c r="P17" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="Q17" t="n">
-        <v>80.23999999999999</v>
+        <v>149.94</v>
       </c>
       <c r="R17" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3214,13 +3202,13 @@
         <v>38.72</v>
       </c>
       <c r="U17" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="V17" t="n">
         <v>71</v>
       </c>
       <c r="W17" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="X17" t="n">
         <v>2</v>
@@ -3241,22 +3229,22 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="AG17" t="n">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="AH17" t="n">
         <v>71</v>
       </c>
       <c r="AI17" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="AJ17" t="n">
         <v>2</v>
@@ -3277,31 +3265,31 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="AS17" t="n">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="AT17" t="n">
-        <v>370</v>
+        <v>71</v>
       </c>
       <c r="AU17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX17" t="n">
-        <v>1</v>
+        <v>410</v>
       </c>
     </row>
     <row r="18">
@@ -3453,19 +3441,19 @@
         <v>377</v>
       </c>
       <c r="AT18" t="n">
-        <v>366</v>
+        <v>45</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV18" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX18" t="n">
-        <v>3</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19">
@@ -3617,19 +3605,19 @@
         <v>318</v>
       </c>
       <c r="AT19" t="n">
-        <v>423</v>
+        <v>150</v>
       </c>
       <c r="AU19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
         <v>2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20">
@@ -3781,19 +3769,19 @@
         <v>307</v>
       </c>
       <c r="AT20" t="n">
-        <v>284</v>
+        <v>15</v>
       </c>
       <c r="AU20" t="n">
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21">
@@ -3945,19 +3933,19 @@
         <v>253</v>
       </c>
       <c r="AT21" t="n">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AX21" t="n">
-        <v>4</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22">
@@ -3992,13 +3980,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -4007,49 +3995,49 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>65.69</v>
+      </c>
+      <c r="R22" t="n">
+        <v>30</v>
+      </c>
+      <c r="S22" t="n">
         <v>7</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4</v>
-      </c>
-      <c r="P22" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>78.88</v>
-      </c>
-      <c r="R22" t="n">
-        <v>25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>6</v>
-      </c>
       <c r="T22" t="n">
-        <v>10.91</v>
+        <v>14.76</v>
       </c>
       <c r="U22" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="V22" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="W22" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="Z22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -4061,31 +4049,31 @@
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="AG22" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AH22" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="AI22" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="AJ22" t="n">
         <v>1</v>
       </c>
       <c r="AK22" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AL22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AM22" t="n">
         <v>0</v>
@@ -4097,31 +4085,31 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="AQ22" t="n">
         <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="AS22" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AT22" t="n">
-        <v>410</v>
+        <v>105</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="AV22" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AW22" t="n">
         <v>1</v>
       </c>
       <c r="AX22" t="n">
-        <v>22</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23">
@@ -4273,19 +4261,19 @@
         <v>423</v>
       </c>
       <c r="AT23" t="n">
-        <v>450</v>
+        <v>141</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV23" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="AW23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24">
@@ -4437,19 +4425,19 @@
         <v>282</v>
       </c>
       <c r="AT24" t="n">
-        <v>359</v>
+        <v>137</v>
       </c>
       <c r="AU24" t="n">
         <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25">
@@ -4601,25 +4589,25 @@
         <v>368</v>
       </c>
       <c r="AT25" t="n">
-        <v>308</v>
+        <v>32</v>
       </c>
       <c r="AU25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>NaN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4648,13 +4636,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>167</v>
+        <v>36</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -4663,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4672,40 +4660,40 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="Q26" t="n">
-        <v>217.95</v>
+        <v>40.82</v>
       </c>
       <c r="R26" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="S26" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>96.97</v>
+        <v>4.08</v>
       </c>
       <c r="U26" t="n">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="V26" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="X26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -4717,31 +4705,31 @@
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="AG26" t="n">
-        <v>309</v>
+        <v>70</v>
       </c>
       <c r="AH26" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="AJ26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
         <v>0</v>
@@ -4753,31 +4741,31 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="AS26" t="n">
-        <v>307</v>
+        <v>70</v>
       </c>
       <c r="AT26" t="n">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -4929,19 +4917,19 @@
         <v>387</v>
       </c>
       <c r="AT27" t="n">
-        <v>342</v>
+        <v>56</v>
       </c>
       <c r="AU27" t="n">
         <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AW27" t="n">
         <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>3</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28">
@@ -5093,10 +5081,10 @@
         <v>375</v>
       </c>
       <c r="AT28" t="n">
-        <v>384</v>
+        <v>109</v>
       </c>
       <c r="AU28" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AV28" t="n">
         <v>0</v>
@@ -5105,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29">
@@ -5257,19 +5245,19 @@
         <v>343</v>
       </c>
       <c r="AT29" t="n">
-        <v>357</v>
+        <v>133</v>
       </c>
       <c r="AU29" t="n">
         <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30">
@@ -5421,19 +5409,19 @@
         <v>380</v>
       </c>
       <c r="AT30" t="n">
-        <v>457</v>
+        <v>139</v>
       </c>
       <c r="AU30" t="n">
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW30" t="n">
         <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
@@ -5585,19 +5573,19 @@
         <v>201</v>
       </c>
       <c r="AT31" t="n">
-        <v>315</v>
+        <v>3</v>
       </c>
       <c r="AU31" t="n">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="AV31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AW31" t="n">
         <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32">
@@ -5749,19 +5737,19 @@
         <v>281</v>
       </c>
       <c r="AT32" t="n">
-        <v>308</v>
+        <v>134</v>
       </c>
       <c r="AU32" t="n">
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33">
@@ -5913,19 +5901,19 @@
         <v>282</v>
       </c>
       <c r="AT33" t="n">
-        <v>365</v>
+        <v>156</v>
       </c>
       <c r="AU33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV33" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34">
@@ -6077,19 +6065,19 @@
         <v>450</v>
       </c>
       <c r="AT34" t="n">
-        <v>410</v>
+        <v>126</v>
       </c>
       <c r="AU34" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AV34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
     </row>
     <row r="35">
@@ -6241,19 +6229,19 @@
         <v>243</v>
       </c>
       <c r="AT35" t="n">
-        <v>303</v>
+        <v>131</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36">
@@ -6405,19 +6393,19 @@
         <v>477</v>
       </c>
       <c r="AT36" t="n">
-        <v>412</v>
+        <v>93</v>
       </c>
       <c r="AU36" t="n">
         <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>4</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37">
@@ -6569,19 +6557,19 @@
         <v>518</v>
       </c>
       <c r="AT37" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
         <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
         <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
     </row>
     <row r="38">
@@ -6612,7 +6600,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6733,19 +6721,19 @@
         <v>365</v>
       </c>
       <c r="AT38" t="n">
-        <v>453</v>
+        <v>122</v>
       </c>
       <c r="AU38" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AV38" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39">
@@ -6776,7 +6764,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6897,19 +6885,19 @@
         <v>313</v>
       </c>
       <c r="AT39" t="n">
-        <v>445</v>
+        <v>152</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AV39" t="n">
         <v>4</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40">
@@ -7061,19 +7049,19 @@
         <v>399</v>
       </c>
       <c r="AT40" t="n">
-        <v>379</v>
+        <v>86</v>
       </c>
       <c r="AU40" t="n">
         <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
         <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41">
@@ -7225,19 +7213,19 @@
         <v>350</v>
       </c>
       <c r="AT41" t="n">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AU41" t="n">
         <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AW41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42">
@@ -7389,19 +7377,19 @@
         <v>387</v>
       </c>
       <c r="AT42" t="n">
-        <v>371</v>
+        <v>127</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AV42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW42" t="n">
         <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43">
@@ -7553,7 +7541,7 @@
         <v>388</v>
       </c>
       <c r="AT43" t="n">
-        <v>331</v>
+        <v>42</v>
       </c>
       <c r="AU43" t="n">
         <v>0</v>
@@ -7562,10 +7550,10 @@
         <v>13</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX43" t="n">
-        <v>1</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44">
@@ -7717,7 +7705,7 @@
         <v>381</v>
       </c>
       <c r="AT44" t="n">
-        <v>301</v>
+        <v>12</v>
       </c>
       <c r="AU44" t="n">
         <v>0</v>
@@ -7726,51 +7714,51 @@
         <v>9</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX44" t="n">
-        <v>10</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fitrianti Tadete</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>fitriantitadete68@gmail.com</t>
+          <t>fransiskapaolin@gmail.com</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>derlanmalawere92@gmail.com</t>
+          <t>anthymanambe8@gmail.com</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(092) TAHUNA BARAT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -7779,7 +7767,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -7791,150 +7779,150 @@
         <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>156</v>
+        <v>94</v>
       </c>
       <c r="Q45" t="n">
-        <v>257.54</v>
+        <v>335.62</v>
       </c>
       <c r="R45" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="T45" t="n">
-        <v>83.23</v>
+        <v>81.35000000000001</v>
       </c>
       <c r="U45" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="V45" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="W45" t="n">
-        <v>329</v>
+        <v>236</v>
       </c>
       <c r="X45" t="n">
         <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF45" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="AG45" t="n">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="AH45" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AI45" t="n">
-        <v>329</v>
+        <v>236</v>
       </c>
       <c r="AJ45" t="n">
         <v>1</v>
       </c>
       <c r="AK45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM45" t="n">
         <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AR45" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="AS45" t="n">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="AT45" t="n">
-        <v>355</v>
+        <v>146</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX45" t="n">
-        <v>2</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>fransiskapaolin@gmail.com</t>
+          <t>frzfrz130293@gmail.com</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>anthymanambe8@gmail.com</t>
+          <t>yanfwpadang84@gmail.com</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(092) TAHUNA BARAT</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>295</v>
+        <v>101</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -7943,49 +7931,49 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
+        <v>19</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
         <v>7</v>
       </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1</v>
-      </c>
       <c r="P46" t="n">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="Q46" t="n">
-        <v>335.62</v>
+        <v>85.45</v>
       </c>
       <c r="R46" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="S46" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>81.35000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="U46" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="V46" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="W46" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="Z46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -7997,31 +7985,31 @@
         <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="AE46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>477</v>
+        <v>433</v>
       </c>
       <c r="AG46" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="AH46" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AI46" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="AL46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
         <v>0</v>
@@ -8033,72 +8021,72 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="AQ46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>477</v>
+        <v>432</v>
       </c>
       <c r="AS46" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="AT46" t="n">
-        <v>434</v>
+        <v>132</v>
       </c>
       <c r="AU46" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AV46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
         <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>frzfrz130293@gmail.com</t>
+          <t>geovanimonok34@gmail.com</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>B. Lenskar Diamanis</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>yanfwpadang84@gmail.com</t>
+          <t>lenskardiamaniz@gmail.com</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(080) MANGANITU</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>101</v>
+        <v>219</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -8107,7 +8095,7 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -8116,153 +8104,153 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="Q47" t="n">
-        <v>85.45</v>
+        <v>177.96</v>
       </c>
       <c r="R47" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="T47" t="n">
-        <v>9.09</v>
+        <v>73.36</v>
       </c>
       <c r="U47" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="V47" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="W47" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Y47" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="AG47" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AH47" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="AI47" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AK47" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM47" t="n">
         <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AQ47" t="n">
         <v>0</v>
       </c>
       <c r="AR47" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AS47" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AT47" t="n">
-        <v>375</v>
+        <v>128</v>
       </c>
       <c r="AU47" t="n">
         <v>1</v>
       </c>
       <c r="AV47" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>geovanimonok34@gmail.com</t>
+          <t>ghenovhepaparaso@gmail.com</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B. Lenskar Diamanis</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>lenskardiamaniz@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(080) MANGANITU</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>27</v>
+        <v>209</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>219</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -8271,85 +8259,85 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
+        <v>54</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>39</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>17</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="U48" t="n">
+        <v>41</v>
+      </c>
+      <c r="V48" t="n">
+        <v>121</v>
+      </c>
+      <c r="W48" t="n">
+        <v>334</v>
+      </c>
+      <c r="X48" t="n">
         <v>4</v>
       </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>177.96</v>
-      </c>
-      <c r="R48" t="n">
-        <v>36</v>
-      </c>
-      <c r="S48" t="n">
-        <v>40</v>
-      </c>
-      <c r="T48" t="n">
-        <v>73.36</v>
-      </c>
-      <c r="U48" t="n">
-        <v>29</v>
-      </c>
-      <c r="V48" t="n">
-        <v>128</v>
-      </c>
-      <c r="W48" t="n">
-        <v>218</v>
-      </c>
-      <c r="X48" t="n">
-        <v>35</v>
-      </c>
       <c r="Y48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>485</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>364</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>121</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>334</v>
+      </c>
+      <c r="AJ48" t="n">
         <v>4</v>
       </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>428</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>299</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>128</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>218</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>35</v>
-      </c>
       <c r="AK48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
         <v>0</v>
@@ -8361,19 +8349,19 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR48" t="n">
-        <v>428</v>
+        <v>485</v>
       </c>
       <c r="AS48" t="n">
-        <v>299</v>
+        <v>364</v>
       </c>
       <c r="AT48" t="n">
-        <v>363</v>
+        <v>121</v>
       </c>
       <c r="AU48" t="n">
         <v>0</v>
@@ -8382,215 +8370,215 @@
         <v>4</v>
       </c>
       <c r="AW48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ghenovhepaparaso@gmail.com</t>
+          <t>gracedorongpangalo11@gmail.com</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>fianemansauda89@gmail.com</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>209</v>
+        <v>27</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
+        <v>362</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>6</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>10</v>
+      </c>
+      <c r="P49" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>229.45</v>
+      </c>
+      <c r="R49" t="n">
+        <v>56</v>
+      </c>
+      <c r="S49" t="n">
+        <v>24</v>
+      </c>
+      <c r="T49" t="n">
+        <v>93.84999999999999</v>
+      </c>
+      <c r="U49" t="n">
+        <v>80</v>
+      </c>
+      <c r="V49" t="n">
+        <v>178</v>
+      </c>
+      <c r="W49" t="n">
+        <v>242</v>
+      </c>
+      <c r="X49" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
         <v>2</v>
       </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>54</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>39</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>17</v>
-      </c>
-      <c r="S49" t="n">
-        <v>1</v>
-      </c>
-      <c r="T49" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="U49" t="n">
-        <v>41</v>
-      </c>
-      <c r="V49" t="n">
-        <v>121</v>
-      </c>
-      <c r="W49" t="n">
-        <v>334</v>
-      </c>
-      <c r="X49" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
       <c r="AC49" t="n">
         <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AE49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF49" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AG49" t="n">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="AH49" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="AI49" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="AJ49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK49" t="n">
         <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AM49" t="n">
         <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR49" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AS49" t="n">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="AT49" t="n">
-        <v>411</v>
+        <v>178</v>
       </c>
       <c r="AU49" t="n">
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>gracedorongpangalo11@gmail.com</t>
+          <t>greispangandaheng@gmail.com</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>fianemansauda89@gmail.com</t>
+          <t>novdeinarifbongkitang@gmail.com</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(050) TAMAKO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>362</v>
+        <v>215</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -8599,326 +8587,326 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="O50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P50" t="n">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="Q50" t="n">
-        <v>229.45</v>
+        <v>144.82</v>
       </c>
       <c r="R50" t="n">
+        <v>30</v>
+      </c>
+      <c r="S50" t="n">
+        <v>89</v>
+      </c>
+      <c r="T50" t="n">
+        <v>142.89</v>
+      </c>
+      <c r="U50" t="n">
         <v>56</v>
       </c>
-      <c r="S50" t="n">
-        <v>24</v>
-      </c>
-      <c r="T50" t="n">
-        <v>93.84999999999999</v>
-      </c>
-      <c r="U50" t="n">
-        <v>80</v>
-      </c>
       <c r="V50" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="W50" t="n">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="X50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AE50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="AG50" t="n">
-        <v>298</v>
+        <v>460</v>
       </c>
       <c r="AH50" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="AI50" t="n">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="AJ50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AM50" t="n">
         <v>0</v>
       </c>
       <c r="AN50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AQ50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR50" t="n">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="AS50" t="n">
-        <v>298</v>
+        <v>460</v>
       </c>
       <c r="AT50" t="n">
-        <v>372</v>
+        <v>61</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AV50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>greispangandaheng@gmail.com</t>
+          <t>hamendahasrita@gmail.com</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>novdeinarifbongkitang@gmail.com</t>
+          <t>novrilleymumu11@gmail.com</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(050) TAMAKO</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G51" t="n">
+        <v>32</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>257</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>9</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>5</v>
+      </c>
+      <c r="P51" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>193.94</v>
+      </c>
+      <c r="R51" t="n">
+        <v>64</v>
+      </c>
+      <c r="S51" t="n">
+        <v>82</v>
+      </c>
+      <c r="T51" t="n">
+        <v>98.12</v>
+      </c>
+      <c r="U51" t="n">
+        <v>90</v>
+      </c>
+      <c r="V51" t="n">
+        <v>89</v>
+      </c>
+      <c r="W51" t="n">
+        <v>331</v>
+      </c>
+      <c r="X51" t="n">
         <v>8</v>
       </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>215</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>2</v>
-      </c>
-      <c r="M51" t="n">
-        <v>2</v>
-      </c>
-      <c r="N51" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="O51" t="n">
-        <v>7</v>
-      </c>
-      <c r="P51" t="n">
-        <v>109</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>144.82</v>
-      </c>
-      <c r="R51" t="n">
-        <v>30</v>
-      </c>
-      <c r="S51" t="n">
+      <c r="Y51" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>482</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>390</v>
+      </c>
+      <c r="AH51" t="n">
         <v>89</v>
       </c>
-      <c r="T51" t="n">
-        <v>142.89</v>
-      </c>
-      <c r="U51" t="n">
-        <v>56</v>
-      </c>
-      <c r="V51" t="n">
-        <v>61</v>
-      </c>
-      <c r="W51" t="n">
-        <v>398</v>
-      </c>
-      <c r="X51" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z51" t="n">
+      <c r="AI51" t="n">
+        <v>331</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK51" t="n">
         <v>3</v>
       </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>52</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>539</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>460</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>61</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>398</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>18</v>
-      </c>
       <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>50</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>482</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>390</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>89</v>
+      </c>
+      <c r="AU51" t="n">
         <v>3</v>
       </c>
-      <c r="AM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>52</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>539</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>460</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>395</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>0</v>
-      </c>
       <c r="AV51" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AW51" t="n">
         <v>0</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>hamendahasrita@gmail.com</t>
+          <t>hapitudhy@gmail.com</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>novrilleymumu11@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>257</v>
+        <v>117</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -8927,7 +8915,7 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -8936,37 +8924,37 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="Q52" t="n">
-        <v>193.94</v>
+        <v>117.71</v>
       </c>
       <c r="R52" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="S52" t="n">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="T52" t="n">
-        <v>98.12</v>
+        <v>73.81</v>
       </c>
       <c r="U52" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="V52" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="W52" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="X52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -8975,34 +8963,34 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AE52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AG52" t="n">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="AH52" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="AI52" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="AJ52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -9011,28 +8999,28 @@
         <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AS52" t="n">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="AT52" t="n">
-        <v>378</v>
+        <v>104</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV52" t="n">
         <v>0</v>
@@ -9041,28 +9029,28 @@
         <v>0</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>hapitudhy@gmail.com</t>
+          <t>harilamachris23@gmail.com</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>vonnelariunaung77560@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -9076,177 +9064,177 @@
         </is>
       </c>
       <c r="G53" t="n">
+        <v>27</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>207</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>6</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>9</v>
+      </c>
+      <c r="P53" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>280.94</v>
+      </c>
+      <c r="R53" t="n">
         <v>59</v>
       </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>107</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>13</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>4</v>
-      </c>
-      <c r="P53" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>122.14</v>
-      </c>
-      <c r="R53" t="n">
-        <v>38</v>
-      </c>
       <c r="S53" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="T53" t="n">
-        <v>110.41</v>
+        <v>190.93</v>
       </c>
       <c r="U53" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="V53" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="W53" t="n">
-        <v>341</v>
+        <v>219</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y53" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF53" t="n">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="AG53" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="AH53" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="AI53" t="n">
-        <v>341</v>
+        <v>219</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AK53" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AM53" t="n">
         <v>0</v>
       </c>
       <c r="AN53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR53" t="n">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="AS53" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="AT53" t="n">
-        <v>429</v>
+        <v>150</v>
       </c>
       <c r="AU53" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="AV53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AW53" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AX53" t="n">
-        <v>1</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>harilamachris23@gmail.com</t>
+          <t>hshyntike@gmail.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>ningsikarendehi968@gmail.com</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(061) TABUKAN SELATAN TENGAH &amp; (062) TABUKAN SELATAN TENGGARA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erwin &amp; Lalu</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>174</v>
+        <v>258</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -9255,88 +9243,88 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
         <v>7</v>
       </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>2</v>
-      </c>
       <c r="P54" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="R54" t="n">
+        <v>118</v>
+      </c>
+      <c r="S54" t="n">
+        <v>26</v>
+      </c>
+      <c r="T54" t="n">
+        <v>65.31999999999999</v>
+      </c>
+      <c r="U54" t="n">
+        <v>99</v>
+      </c>
+      <c r="V54" t="n">
+        <v>83</v>
+      </c>
+      <c r="W54" t="n">
+        <v>235</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
         <v>78</v>
       </c>
-      <c r="Q54" t="n">
-        <v>230.06</v>
-      </c>
-      <c r="R54" t="n">
-        <v>45</v>
-      </c>
-      <c r="S54" t="n">
-        <v>47</v>
-      </c>
-      <c r="T54" t="n">
-        <v>199.27</v>
-      </c>
-      <c r="U54" t="n">
-        <v>34</v>
-      </c>
-      <c r="V54" t="n">
-        <v>201</v>
-      </c>
-      <c r="W54" t="n">
-        <v>166</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>31</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>12</v>
-      </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF54" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="AG54" t="n">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="AH54" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="AJ54" t="n">
         <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN54" t="n">
         <v>0</v>
@@ -9345,72 +9333,72 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR54" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="AS54" t="n">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="AT54" t="n">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="AU54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX54" t="n">
-        <v>2</v>
+        <v>235</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>hshyntike@gmail.com</t>
+          <t>igirisatia5@gmail.com</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ningsikarendehi968@gmail.com</t>
+          <t>yanfwpadang84@gmail.com</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(061) TABUKAN SELATAN TENGAH &amp; (062) TABUKAN SELATAN TENGGARA</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Erwin &amp; Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>258</v>
+        <v>29</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -9419,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -9428,43 +9416,43 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="P55" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="Q55" t="n">
-        <v>65.01000000000001</v>
+        <v>48.57</v>
       </c>
       <c r="R55" t="n">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="S55" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="T55" t="n">
-        <v>65.31999999999999</v>
+        <v>53.84</v>
       </c>
       <c r="U55" t="n">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="V55" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="W55" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
         <v>0</v>
@@ -9473,34 +9461,34 @@
         <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="AE55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF55" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="AG55" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="AH55" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AI55" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN55" t="n">
         <v>0</v>
@@ -9509,72 +9497,72 @@
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="AQ55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AR55" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="AS55" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="AT55" t="n">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AV55" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AW55" t="n">
         <v>0</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>403</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>igirisatia5@gmail.com</t>
+          <t>indrydorthea@gmail.com</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>yanfwpadang84@gmail.com</t>
+          <t>jekirvenkildompas@gmail.com</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>29</v>
+        <v>411</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -9583,49 +9571,49 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="O56" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="P56" t="n">
+        <v>109</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>192.51</v>
+      </c>
+      <c r="R56" t="n">
+        <v>51</v>
+      </c>
+      <c r="S56" t="n">
+        <v>90</v>
+      </c>
+      <c r="T56" t="n">
+        <v>146.1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>101</v>
+      </c>
+      <c r="V56" t="n">
+        <v>148</v>
+      </c>
+      <c r="W56" t="n">
+        <v>215</v>
+      </c>
+      <c r="X56" t="n">
+        <v>73</v>
+      </c>
+      <c r="Y56" t="n">
         <v>17</v>
       </c>
-      <c r="Q56" t="n">
-        <v>48.57</v>
-      </c>
-      <c r="R56" t="n">
-        <v>14</v>
-      </c>
-      <c r="S56" t="n">
-        <v>18</v>
-      </c>
-      <c r="T56" t="n">
-        <v>53.84</v>
-      </c>
-      <c r="U56" t="n">
-        <v>48</v>
-      </c>
-      <c r="V56" t="n">
-        <v>160</v>
-      </c>
-      <c r="W56" t="n">
-        <v>403</v>
-      </c>
-      <c r="X56" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>45</v>
-      </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -9637,31 +9625,31 @@
         <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="AG56" t="n">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="AH56" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="AI56" t="n">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="AJ56" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="AK56" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM56" t="n">
         <v>0</v>
@@ -9673,72 +9661,72 @@
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="AQ56" t="n">
         <v>1</v>
       </c>
       <c r="AR56" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="AS56" t="n">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="AT56" t="n">
-        <v>420</v>
+        <v>148</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AV56" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>indrydorthea@gmail.com</t>
+          <t>iyanmaniku1@gmail.com</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jekirvenkildompas@gmail.com</t>
+          <t>derlanmalawere92@gmail.com</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>411</v>
+        <v>312</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -9747,49 +9735,49 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>257.54</v>
+      </c>
+      <c r="R57" t="n">
+        <v>34</v>
+      </c>
+      <c r="S57" t="n">
+        <v>50</v>
+      </c>
+      <c r="T57" t="n">
+        <v>83.23</v>
+      </c>
+      <c r="U57" t="n">
+        <v>63</v>
+      </c>
+      <c r="V57" t="n">
+        <v>85</v>
+      </c>
+      <c r="W57" t="n">
+        <v>329</v>
+      </c>
+      <c r="X57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y57" t="n">
         <v>7</v>
       </c>
-      <c r="P57" t="n">
-        <v>109</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>192.51</v>
-      </c>
-      <c r="R57" t="n">
-        <v>51</v>
-      </c>
-      <c r="S57" t="n">
-        <v>90</v>
-      </c>
-      <c r="T57" t="n">
-        <v>146.1</v>
-      </c>
-      <c r="U57" t="n">
-        <v>101</v>
-      </c>
-      <c r="V57" t="n">
-        <v>148</v>
-      </c>
-      <c r="W57" t="n">
-        <v>215</v>
-      </c>
-      <c r="X57" t="n">
-        <v>73</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>17</v>
-      </c>
       <c r="Z57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9801,31 +9789,31 @@
         <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AE57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="AG57" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AH57" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="AI57" t="n">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="AJ57" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="AK57" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AL57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM57" t="n">
         <v>0</v>
@@ -9837,31 +9825,31 @@
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR57" t="n">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="AS57" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AT57" t="n">
-        <v>336</v>
+        <v>85</v>
       </c>
       <c r="AU57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AW57" t="n">
         <v>0</v>
       </c>
       <c r="AX57" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="58">
@@ -10013,19 +10001,19 @@
         <v>267</v>
       </c>
       <c r="AT58" t="n">
-        <v>363</v>
+        <v>194</v>
       </c>
       <c r="AU58" t="n">
         <v>0</v>
       </c>
       <c r="AV58" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX58" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59">
@@ -10177,19 +10165,19 @@
         <v>364</v>
       </c>
       <c r="AT59" t="n">
-        <v>383</v>
+        <v>108</v>
       </c>
       <c r="AU59" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AW59" t="n">
         <v>0</v>
       </c>
       <c r="AX59" t="n">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="60">
@@ -10341,19 +10329,19 @@
         <v>289</v>
       </c>
       <c r="AT60" t="n">
-        <v>377</v>
+        <v>160</v>
       </c>
       <c r="AU60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV60" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="AW60" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX60" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61">
@@ -10505,19 +10493,19 @@
         <v>238</v>
       </c>
       <c r="AT61" t="n">
-        <v>314</v>
+        <v>126</v>
       </c>
       <c r="AU61" t="n">
         <v>0</v>
       </c>
       <c r="AV61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AW61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX61" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62">
@@ -10669,19 +10657,19 @@
         <v>440</v>
       </c>
       <c r="AT62" t="n">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="AU62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV62" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="AW62" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AX62" t="n">
-        <v>6</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63">
@@ -10833,19 +10821,19 @@
         <v>373</v>
       </c>
       <c r="AT63" t="n">
-        <v>324</v>
+        <v>99</v>
       </c>
       <c r="AU63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV63" t="n">
         <v>0</v>
       </c>
       <c r="AW63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX63" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64">
@@ -10997,19 +10985,19 @@
         <v>394</v>
       </c>
       <c r="AT64" t="n">
-        <v>440</v>
+        <v>157</v>
       </c>
       <c r="AU64" t="n">
         <v>0</v>
       </c>
       <c r="AV64" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AW64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX64" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="65">
@@ -11161,19 +11149,19 @@
         <v>357</v>
       </c>
       <c r="AT65" t="n">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="AU65" t="n">
         <v>0</v>
       </c>
       <c r="AV65" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AW65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX65" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66">
@@ -11325,19 +11313,19 @@
         <v>397</v>
       </c>
       <c r="AT66" t="n">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AU66" t="n">
         <v>0</v>
       </c>
       <c r="AV66" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="AW66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX66" t="n">
-        <v>2</v>
+        <v>316</v>
       </c>
     </row>
     <row r="67">
@@ -11489,19 +11477,19 @@
         <v>255</v>
       </c>
       <c r="AT67" t="n">
-        <v>297</v>
+        <v>100</v>
       </c>
       <c r="AU67" t="n">
         <v>0</v>
       </c>
       <c r="AV67" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AW67" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AX67" t="n">
-        <v>1</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68">
@@ -11653,19 +11641,19 @@
         <v>504</v>
       </c>
       <c r="AT68" t="n">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AU68" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AV68" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AW68" t="n">
         <v>1</v>
       </c>
       <c r="AX68" t="n">
-        <v>8</v>
+        <v>448</v>
       </c>
     </row>
     <row r="69">
@@ -11817,19 +11805,19 @@
         <v>300</v>
       </c>
       <c r="AT69" t="n">
-        <v>317</v>
+        <v>101</v>
       </c>
       <c r="AU69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV69" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="AW69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AX69" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70">
@@ -11981,19 +11969,19 @@
         <v>224</v>
       </c>
       <c r="AT70" t="n">
-        <v>306</v>
+        <v>131</v>
       </c>
       <c r="AU70" t="n">
         <v>0</v>
       </c>
       <c r="AV70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW70" t="n">
         <v>0</v>
       </c>
       <c r="AX70" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71">
@@ -12145,19 +12133,19 @@
         <v>441</v>
       </c>
       <c r="AT71" t="n">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="AU71" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AV71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW71" t="n">
         <v>0</v>
       </c>
       <c r="AX71" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
     </row>
     <row r="72">
@@ -12309,19 +12297,19 @@
         <v>578</v>
       </c>
       <c r="AT72" t="n">
-        <v>353</v>
+        <v>3</v>
       </c>
       <c r="AU72" t="n">
         <v>0</v>
       </c>
       <c r="AV72" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AW72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX72" t="n">
-        <v>0</v>
+        <v>492</v>
       </c>
     </row>
     <row r="73">
@@ -12473,19 +12461,19 @@
         <v>331</v>
       </c>
       <c r="AT73" t="n">
-        <v>362</v>
+        <v>105</v>
       </c>
       <c r="AU73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV73" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AW73" t="n">
         <v>0</v>
       </c>
       <c r="AX73" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
     </row>
     <row r="74">
@@ -12637,10 +12625,10 @@
         <v>472</v>
       </c>
       <c r="AT74" t="n">
-        <v>398</v>
+        <v>19</v>
       </c>
       <c r="AU74" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="AV74" t="n">
         <v>0</v>
@@ -12649,7 +12637,7 @@
         <v>0</v>
       </c>
       <c r="AX74" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
     </row>
     <row r="75">
@@ -12801,19 +12789,19 @@
         <v>283</v>
       </c>
       <c r="AT75" t="n">
-        <v>359</v>
+        <v>138</v>
       </c>
       <c r="AU75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV75" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AW75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX75" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76">
@@ -12965,19 +12953,19 @@
         <v>251</v>
       </c>
       <c r="AT76" t="n">
-        <v>357</v>
+        <v>175</v>
       </c>
       <c r="AU76" t="n">
         <v>0</v>
       </c>
       <c r="AV76" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="AW76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX76" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77">
@@ -13129,19 +13117,19 @@
         <v>430</v>
       </c>
       <c r="AT77" t="n">
-        <v>386</v>
+        <v>87</v>
       </c>
       <c r="AU77" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AV77" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AW77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX77" t="n">
-        <v>7</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78">
@@ -13293,19 +13281,19 @@
         <v>306</v>
       </c>
       <c r="AT78" t="n">
-        <v>350</v>
+        <v>114</v>
       </c>
       <c r="AU78" t="n">
         <v>0</v>
       </c>
       <c r="AV78" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="AW78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX78" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79">
@@ -13457,7 +13445,7 @@
         <v>394</v>
       </c>
       <c r="AT79" t="n">
-        <v>319</v>
+        <v>21</v>
       </c>
       <c r="AU79" t="n">
         <v>0</v>
@@ -13466,174 +13454,174 @@
         <v>6</v>
       </c>
       <c r="AW79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX79" t="n">
-        <v>7</v>
+        <v>313</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mery Grace Anabelia Kantohe</t>
+          <t>Aldo Jhon Mesak Bangonang</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>merykantohe979@gmail.com</t>
+          <t>mesakbangonang99@gmail.com</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
+        <v>98</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>4</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>3</v>
+      </c>
+      <c r="P80" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>126.25</v>
+      </c>
+      <c r="R80" t="n">
+        <v>25</v>
+      </c>
+      <c r="S80" t="n">
+        <v>26</v>
+      </c>
+      <c r="T80" t="n">
+        <v>101.23</v>
+      </c>
+      <c r="U80" t="n">
+        <v>46</v>
+      </c>
+      <c r="V80" t="n">
+        <v>211</v>
+      </c>
+      <c r="W80" t="n">
+        <v>108</v>
+      </c>
+      <c r="X80" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>390</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>161</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>213</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>108</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>390</v>
+      </c>
+      <c r="AS80" t="n">
         <v>159</v>
       </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>3</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1</v>
-      </c>
-      <c r="P80" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>102.11</v>
-      </c>
-      <c r="R80" t="n">
-        <v>47</v>
-      </c>
-      <c r="S80" t="n">
-        <v>39</v>
-      </c>
-      <c r="T80" t="n">
-        <v>80.28</v>
-      </c>
-      <c r="U80" t="n">
-        <v>57</v>
-      </c>
-      <c r="V80" t="n">
-        <v>95</v>
-      </c>
-      <c r="W80" t="n">
-        <v>149</v>
-      </c>
-      <c r="X80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD80" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF80" t="n">
-        <v>289</v>
-      </c>
-      <c r="AG80" t="n">
-        <v>194</v>
-      </c>
-      <c r="AH80" t="n">
-        <v>95</v>
-      </c>
-      <c r="AI80" t="n">
-        <v>149</v>
-      </c>
-      <c r="AJ80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL80" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN80" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP80" t="n">
-        <v>42</v>
-      </c>
-      <c r="AQ80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR80" t="n">
-        <v>289</v>
-      </c>
-      <c r="AS80" t="n">
-        <v>194</v>
-      </c>
       <c r="AT80" t="n">
-        <v>263</v>
+        <v>211</v>
       </c>
       <c r="AU80" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AW80" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX80" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="81">
@@ -13785,19 +13773,19 @@
         <v>292</v>
       </c>
       <c r="AT81" t="n">
-        <v>313</v>
+        <v>60</v>
       </c>
       <c r="AU81" t="n">
         <v>0</v>
       </c>
       <c r="AV81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AW81" t="n">
         <v>0</v>
       </c>
       <c r="AX81" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82">
@@ -13949,19 +13937,19 @@
         <v>330</v>
       </c>
       <c r="AT82" t="n">
-        <v>385</v>
+        <v>113</v>
       </c>
       <c r="AU82" t="n">
         <v>0</v>
       </c>
       <c r="AV82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AW82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX82" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
     </row>
     <row r="83">
@@ -14113,19 +14101,19 @@
         <v>299</v>
       </c>
       <c r="AT83" t="n">
-        <v>340</v>
+        <v>159</v>
       </c>
       <c r="AU83" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AV83" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="AW83" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AX83" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84">
@@ -14277,19 +14265,19 @@
         <v>316</v>
       </c>
       <c r="AT84" t="n">
-        <v>378</v>
+        <v>111</v>
       </c>
       <c r="AU84" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AV84" t="n">
         <v>0</v>
       </c>
       <c r="AW84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX84" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85">
@@ -14441,19 +14429,19 @@
         <v>299</v>
       </c>
       <c r="AT85" t="n">
-        <v>367</v>
+        <v>126</v>
       </c>
       <c r="AU85" t="n">
         <v>0</v>
       </c>
       <c r="AV85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AW85" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AX85" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86">
@@ -14605,19 +14593,19 @@
         <v>327</v>
       </c>
       <c r="AT86" t="n">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AU86" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AV86" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW86" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AX86" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="87">
@@ -14769,19 +14757,19 @@
         <v>278</v>
       </c>
       <c r="AT87" t="n">
-        <v>360</v>
+        <v>146</v>
       </c>
       <c r="AU87" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AV87" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AW87" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AX87" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88">
@@ -14933,19 +14921,19 @@
         <v>362</v>
       </c>
       <c r="AT88" t="n">
-        <v>356</v>
+        <v>70</v>
       </c>
       <c r="AU88" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AV88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX88" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="89">
@@ -15097,19 +15085,19 @@
         <v>333</v>
       </c>
       <c r="AT89" t="n">
-        <v>405</v>
+        <v>167</v>
       </c>
       <c r="AU89" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AV89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW89" t="n">
         <v>2</v>
       </c>
-      <c r="AW89" t="n">
-        <v>0</v>
-      </c>
       <c r="AX89" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="90">
@@ -15261,19 +15249,19 @@
         <v>239</v>
       </c>
       <c r="AT90" t="n">
-        <v>301</v>
+        <v>51</v>
       </c>
       <c r="AU90" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AV90" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AW90" t="n">
         <v>0</v>
       </c>
       <c r="AX90" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91">
@@ -15425,19 +15413,19 @@
         <v>316</v>
       </c>
       <c r="AT91" t="n">
-        <v>399</v>
+        <v>127</v>
       </c>
       <c r="AU91" t="n">
         <v>0</v>
       </c>
       <c r="AV91" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AW91" t="n">
         <v>0</v>
       </c>
       <c r="AX91" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
     </row>
     <row r="92">
@@ -15589,19 +15577,19 @@
         <v>360</v>
       </c>
       <c r="AT92" t="n">
-        <v>364</v>
+        <v>108</v>
       </c>
       <c r="AU92" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV92" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW92" t="n">
         <v>0</v>
       </c>
       <c r="AX92" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
     </row>
     <row r="93">
@@ -15753,19 +15741,19 @@
         <v>381</v>
       </c>
       <c r="AT93" t="n">
-        <v>335</v>
+        <v>42</v>
       </c>
       <c r="AU93" t="n">
         <v>0</v>
       </c>
       <c r="AV93" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AW93" t="n">
         <v>0</v>
       </c>
       <c r="AX93" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
     </row>
     <row r="94">
@@ -15917,10 +15905,10 @@
         <v>278</v>
       </c>
       <c r="AT94" t="n">
-        <v>373</v>
+        <v>164</v>
       </c>
       <c r="AU94" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="AV94" t="n">
         <v>4</v>
@@ -15929,7 +15917,7 @@
         <v>0</v>
       </c>
       <c r="AX94" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95">
@@ -16081,19 +16069,19 @@
         <v>382</v>
       </c>
       <c r="AT95" t="n">
-        <v>356</v>
+        <v>47</v>
       </c>
       <c r="AU95" t="n">
         <v>0</v>
       </c>
       <c r="AV95" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AW95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX95" t="n">
-        <v>3</v>
+        <v>325</v>
       </c>
     </row>
     <row r="96">
@@ -16245,19 +16233,19 @@
         <v>366</v>
       </c>
       <c r="AT96" t="n">
-        <v>282</v>
+        <v>30</v>
       </c>
       <c r="AU96" t="n">
         <v>0</v>
       </c>
       <c r="AV96" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="AW96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX96" t="n">
-        <v>1</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97">
@@ -16409,19 +16397,19 @@
         <v>360</v>
       </c>
       <c r="AT97" t="n">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="AU97" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="AV97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW97" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX97" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="98">
@@ -16573,19 +16561,19 @@
         <v>248</v>
       </c>
       <c r="AT98" t="n">
-        <v>367</v>
+        <v>152</v>
       </c>
       <c r="AU98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV98" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="AW98" t="n">
         <v>0</v>
       </c>
       <c r="AX98" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99">
@@ -16737,19 +16725,19 @@
         <v>347</v>
       </c>
       <c r="AT99" t="n">
-        <v>321</v>
+        <v>87</v>
       </c>
       <c r="AU99" t="n">
         <v>0</v>
       </c>
       <c r="AV99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX99" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
     </row>
     <row r="100">
@@ -16901,19 +16889,19 @@
         <v>277</v>
       </c>
       <c r="AT100" t="n">
-        <v>343</v>
+        <v>161</v>
       </c>
       <c r="AU100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV100" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AW100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX100" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="101">
@@ -17065,19 +17053,19 @@
         <v>399</v>
       </c>
       <c r="AT101" t="n">
-        <v>455</v>
+        <v>134</v>
       </c>
       <c r="AU101" t="n">
         <v>0</v>
       </c>
       <c r="AV101" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AW101" t="n">
         <v>0</v>
       </c>
       <c r="AX101" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
     </row>
     <row r="102">
@@ -17108,7 +17096,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -17229,19 +17217,19 @@
         <v>318</v>
       </c>
       <c r="AT102" t="n">
-        <v>472</v>
+        <v>192</v>
       </c>
       <c r="AU102" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AV102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW102" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX102" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103">
@@ -17393,19 +17381,19 @@
         <v>427</v>
       </c>
       <c r="AT103" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="AU103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV103" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AW103" t="n">
         <v>0</v>
       </c>
       <c r="AX103" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
     </row>
     <row r="104">
@@ -17436,7 +17424,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -17557,19 +17545,19 @@
         <v>296</v>
       </c>
       <c r="AT104" t="n">
-        <v>422</v>
+        <v>139</v>
       </c>
       <c r="AU104" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AV104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW104" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX104" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="105">
@@ -17604,13 +17592,13 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -17619,7 +17607,7 @@
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -17631,28 +17619,28 @@
         <v>11</v>
       </c>
       <c r="P105" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="Q105" t="n">
-        <v>111.36</v>
+        <v>115.79</v>
       </c>
       <c r="R105" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="S105" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="T105" t="n">
-        <v>156.96</v>
+        <v>193.56</v>
       </c>
       <c r="U105" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="V105" t="n">
         <v>87</v>
       </c>
       <c r="W105" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="X105" t="n">
         <v>16</v>
@@ -17673,22 +17661,22 @@
         <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="AE105" t="n">
         <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="AG105" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="AH105" t="n">
         <v>87</v>
       </c>
       <c r="AI105" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="AJ105" t="n">
         <v>16</v>
@@ -17709,31 +17697,31 @@
         <v>0</v>
       </c>
       <c r="AP105" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="AQ105" t="n">
         <v>0</v>
       </c>
       <c r="AR105" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="AS105" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="AT105" t="n">
-        <v>391</v>
+        <v>87</v>
       </c>
       <c r="AU105" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV105" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AW105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AX105" t="n">
-        <v>5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="106">
@@ -17885,19 +17873,19 @@
         <v>395</v>
       </c>
       <c r="AT106" t="n">
-        <v>366</v>
+        <v>113</v>
       </c>
       <c r="AU106" t="n">
         <v>1</v>
       </c>
       <c r="AV106" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="AW106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX106" t="n">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="107">
@@ -18049,19 +18037,19 @@
         <v>307</v>
       </c>
       <c r="AT107" t="n">
-        <v>322</v>
+        <v>72</v>
       </c>
       <c r="AU107" t="n">
         <v>0</v>
       </c>
       <c r="AV107" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW107" t="n">
         <v>0</v>
       </c>
       <c r="AX107" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
     </row>
     <row r="108">
@@ -18213,19 +18201,19 @@
         <v>368</v>
       </c>
       <c r="AT108" t="n">
-        <v>324</v>
+        <v>32</v>
       </c>
       <c r="AU108" t="n">
         <v>0</v>
       </c>
       <c r="AV108" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AW108" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AX108" t="n">
-        <v>5</v>
+        <v>304</v>
       </c>
     </row>
     <row r="109">
@@ -18377,10 +18365,10 @@
         <v>313</v>
       </c>
       <c r="AT109" t="n">
-        <v>407</v>
+        <v>193</v>
       </c>
       <c r="AU109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV109" t="n">
         <v>2</v>
@@ -18389,7 +18377,7 @@
         <v>0</v>
       </c>
       <c r="AX109" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
     </row>
     <row r="110">
@@ -18541,10 +18529,10 @@
         <v>404</v>
       </c>
       <c r="AT110" t="n">
-        <v>507</v>
+        <v>213</v>
       </c>
       <c r="AU110" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV110" t="n">
         <v>0</v>
@@ -18553,7 +18541,7 @@
         <v>3</v>
       </c>
       <c r="AX110" t="n">
-        <v>2</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111">
@@ -18705,19 +18693,19 @@
         <v>307</v>
       </c>
       <c r="AT111" t="n">
-        <v>294</v>
+        <v>109</v>
       </c>
       <c r="AU111" t="n">
         <v>0</v>
       </c>
       <c r="AV111" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AW111" t="n">
         <v>0</v>
       </c>
       <c r="AX111" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
     </row>
     <row r="112">
@@ -18869,19 +18857,19 @@
         <v>262</v>
       </c>
       <c r="AT112" t="n">
-        <v>403</v>
+        <v>178</v>
       </c>
       <c r="AU112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX112" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
     </row>
     <row r="113">
@@ -19033,19 +19021,19 @@
         <v>442</v>
       </c>
       <c r="AT113" t="n">
-        <v>362</v>
+        <v>87</v>
       </c>
       <c r="AU113" t="n">
         <v>0</v>
       </c>
       <c r="AV113" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="AW113" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AX113" t="n">
-        <v>2</v>
+        <v>286</v>
       </c>
     </row>
     <row r="114">
@@ -19197,19 +19185,19 @@
         <v>561</v>
       </c>
       <c r="AT114" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="AU114" t="n">
         <v>0</v>
       </c>
       <c r="AV114" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AW114" t="n">
         <v>0</v>
       </c>
       <c r="AX114" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
     </row>
     <row r="115">
@@ -19361,19 +19349,19 @@
         <v>271</v>
       </c>
       <c r="AT115" t="n">
-        <v>344</v>
+        <v>162</v>
       </c>
       <c r="AU115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW115" t="n">
         <v>0</v>
       </c>
       <c r="AX115" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116">
@@ -19525,60 +19513,60 @@
         <v>292</v>
       </c>
       <c r="AT116" t="n">
-        <v>333</v>
+        <v>102</v>
       </c>
       <c r="AU116" t="n">
         <v>0</v>
       </c>
       <c r="AV116" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AW116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AX116" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>stivfrancois@gmail.com</t>
+          <t>srirahayudurumias@gmail.com</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fresly Jeica Manangkoda</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>fmanangkoda12@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(050) TAMAKO</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -19596,46 +19584,46 @@
         <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P117" t="n">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="Q117" t="n">
-        <v>246.17</v>
+        <v>102.11</v>
       </c>
       <c r="R117" t="n">
+        <v>47</v>
+      </c>
+      <c r="S117" t="n">
         <v>39</v>
       </c>
-      <c r="S117" t="n">
-        <v>72</v>
-      </c>
       <c r="T117" t="n">
-        <v>204.71</v>
+        <v>80.28</v>
       </c>
       <c r="U117" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="V117" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="W117" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="X117" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y117" t="n">
         <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -19647,31 +19635,31 @@
         <v>0</v>
       </c>
       <c r="AF117" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="AG117" t="n">
-        <v>371</v>
+        <v>194</v>
       </c>
       <c r="AH117" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="AI117" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="AJ117" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AK117" t="n">
         <v>0</v>
       </c>
       <c r="AL117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM117" t="n">
         <v>0</v>
       </c>
       <c r="AN117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO117" t="n">
         <v>0</v>
@@ -19683,66 +19671,66 @@
         <v>0</v>
       </c>
       <c r="AR117" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="AS117" t="n">
-        <v>371</v>
+        <v>194</v>
       </c>
       <c r="AT117" t="n">
-        <v>364</v>
+        <v>95</v>
       </c>
       <c r="AU117" t="n">
         <v>0</v>
       </c>
       <c r="AV117" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AW117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX117" t="n">
-        <v>6</v>
+        <v>149</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>sulastribwnti@gmail.com</t>
+          <t>stivfrancois@gmail.com</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sutrisno Sariang</t>
+          <t>Fresly Jeica Manangkoda</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>sutrisnosariang90@gmail.com</t>
+          <t>fmanangkoda12@gmail.com</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(050) TAMAKO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -19763,31 +19751,31 @@
         <v>7</v>
       </c>
       <c r="P118" t="n">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="Q118" t="n">
-        <v>134.93</v>
+        <v>246.17</v>
       </c>
       <c r="R118" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="S118" t="n">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="T118" t="n">
-        <v>136.08</v>
+        <v>204.71</v>
       </c>
       <c r="U118" t="n">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="V118" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="W118" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="X118" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y118" t="n">
         <v>0</v>
@@ -19808,22 +19796,22 @@
         <v>42</v>
       </c>
       <c r="AE118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF118" t="n">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="AG118" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="AH118" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="AI118" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="AJ118" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AK118" t="n">
         <v>0</v>
@@ -19844,69 +19832,69 @@
         <v>42</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR118" t="n">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="AS118" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="AT118" t="n">
-        <v>378</v>
+        <v>64</v>
       </c>
       <c r="AU118" t="n">
         <v>0</v>
       </c>
       <c r="AV118" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AW118" t="n">
         <v>0</v>
       </c>
       <c r="AX118" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>sunarditamado2@gmail.com</t>
+          <t>sulastribwnti@gmail.com</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Sutrisno Sariang</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>sutrisnosariang90@gmail.com</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -19915,43 +19903,43 @@
         <v>0</v>
       </c>
       <c r="L119" t="n">
+        <v>3</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
         <v>7</v>
       </c>
-      <c r="M119" t="n">
-        <v>0</v>
-      </c>
-      <c r="N119" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" t="n">
-        <v>2</v>
-      </c>
       <c r="P119" t="n">
-        <v>190</v>
+        <v>89</v>
       </c>
       <c r="Q119" t="n">
-        <v>181.64</v>
+        <v>134.93</v>
       </c>
       <c r="R119" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="S119" t="n">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="T119" t="n">
-        <v>60.26</v>
+        <v>136.08</v>
       </c>
       <c r="U119" t="n">
-        <v>89</v>
+        <v>174</v>
       </c>
       <c r="V119" t="n">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="W119" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="X119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y119" t="n">
         <v>0</v>
@@ -19963,31 +19951,31 @@
         <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="AE119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF119" t="n">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="AG119" t="n">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="AH119" t="n">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="AI119" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="AJ119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK119" t="n">
         <v>0</v>
@@ -19999,78 +19987,78 @@
         <v>0</v>
       </c>
       <c r="AN119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO119" t="n">
         <v>0</v>
       </c>
       <c r="AP119" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="AQ119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AR119" t="n">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="AS119" t="n">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="AT119" t="n">
-        <v>420</v>
+        <v>134</v>
       </c>
       <c r="AU119" t="n">
         <v>0</v>
       </c>
       <c r="AV119" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW119" t="n">
         <v>0</v>
       </c>
       <c r="AX119" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>tangkabiringananti@gmail.com</t>
+          <t>sunarditamado2@gmail.com</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -20079,7 +20067,7 @@
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -20088,34 +20076,34 @@
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P120" t="n">
-        <v>23</v>
+        <v>190</v>
       </c>
       <c r="Q120" t="n">
-        <v>29.04</v>
+        <v>181.64</v>
       </c>
       <c r="R120" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="S120" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="T120" t="n">
-        <v>82.38</v>
+        <v>60.26</v>
       </c>
       <c r="U120" t="n">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="V120" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="W120" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="X120" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y120" t="n">
         <v>0</v>
@@ -20127,31 +20115,31 @@
         <v>0</v>
       </c>
       <c r="AB120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>58</v>
+      </c>
+      <c r="AE120" t="n">
         <v>3</v>
       </c>
-      <c r="AC120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD120" t="n">
-        <v>96</v>
-      </c>
-      <c r="AE120" t="n">
-        <v>0</v>
-      </c>
       <c r="AF120" t="n">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="AG120" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="AH120" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="AI120" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="AJ120" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AK120" t="n">
         <v>0</v>
@@ -20163,78 +20151,78 @@
         <v>0</v>
       </c>
       <c r="AN120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>58</v>
+      </c>
+      <c r="AQ120" t="n">
         <v>3</v>
       </c>
-      <c r="AO120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP120" t="n">
-        <v>96</v>
-      </c>
-      <c r="AQ120" t="n">
-        <v>0</v>
-      </c>
       <c r="AR120" t="n">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="AS120" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="AT120" t="n">
-        <v>430</v>
+        <v>44</v>
       </c>
       <c r="AU120" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW120" t="n">
         <v>0</v>
       </c>
       <c r="AX120" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>tangkabiringanayen70@gmail.com</t>
+          <t>tangkabiringananti@gmail.com</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>georgemulersasiangsasiang@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>178</v>
+        <v>23</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>18</v>
+        <v>223</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -20243,82 +20231,82 @@
         <v>0</v>
       </c>
       <c r="L121" t="n">
+        <v>5</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>12</v>
+      </c>
+      <c r="P121" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="R121" t="n">
         <v>39</v>
       </c>
-      <c r="M121" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" t="n">
-        <v>79</v>
-      </c>
-      <c r="P121" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>20</v>
-      </c>
-      <c r="R121" t="n">
-        <v>25</v>
-      </c>
       <c r="S121" t="n">
+        <v>74</v>
+      </c>
+      <c r="T121" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="U121" t="n">
+        <v>115</v>
+      </c>
+      <c r="V121" t="n">
+        <v>164</v>
+      </c>
+      <c r="W121" t="n">
+        <v>266</v>
+      </c>
+      <c r="X121" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB121" t="n">
         <v>3</v>
       </c>
-      <c r="T121" t="n">
-        <v>12.55</v>
-      </c>
-      <c r="U121" t="n">
-        <v>45</v>
-      </c>
-      <c r="V121" t="n">
-        <v>185</v>
-      </c>
-      <c r="W121" t="n">
-        <v>242</v>
-      </c>
-      <c r="X121" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y121" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB121" t="n">
-        <v>0</v>
-      </c>
       <c r="AC121" t="n">
         <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="AE121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF121" t="n">
-        <v>479</v>
+        <v>544</v>
       </c>
       <c r="AG121" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="AH121" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="AI121" t="n">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="AJ121" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AK121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL121" t="n">
         <v>0</v>
@@ -20327,87 +20315,87 @@
         <v>0</v>
       </c>
       <c r="AN121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO121" t="n">
         <v>0</v>
       </c>
       <c r="AP121" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR121" t="n">
-        <v>479</v>
+        <v>544</v>
       </c>
       <c r="AS121" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="AT121" t="n">
-        <v>379</v>
+        <v>164</v>
       </c>
       <c r="AU121" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV121" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW121" t="n">
         <v>0</v>
       </c>
       <c r="AX121" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>tentangsangihe@gmail.com</t>
+          <t>tangkabiringanayen70@gmail.com</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>georgemulersasiangsasiang@gmail.com</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
@@ -20416,38 +20404,38 @@
         <v>0</v>
       </c>
       <c r="O122" t="n">
+        <v>79</v>
+      </c>
+      <c r="P122" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>20</v>
+      </c>
+      <c r="R122" t="n">
+        <v>25</v>
+      </c>
+      <c r="S122" t="n">
+        <v>3</v>
+      </c>
+      <c r="T122" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="U122" t="n">
+        <v>45</v>
+      </c>
+      <c r="V122" t="n">
+        <v>185</v>
+      </c>
+      <c r="W122" t="n">
+        <v>242</v>
+      </c>
+      <c r="X122" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y122" t="n">
         <v>2</v>
       </c>
-      <c r="P122" t="n">
-        <v>101</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>134.75</v>
-      </c>
-      <c r="R122" t="n">
-        <v>90</v>
-      </c>
-      <c r="S122" t="n">
-        <v>34</v>
-      </c>
-      <c r="T122" t="n">
-        <v>57.46</v>
-      </c>
-      <c r="U122" t="n">
-        <v>49</v>
-      </c>
-      <c r="V122" t="n">
-        <v>126</v>
-      </c>
-      <c r="W122" t="n">
-        <v>256</v>
-      </c>
-      <c r="X122" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>0</v>
-      </c>
       <c r="Z122" t="n">
         <v>0</v>
       </c>
@@ -20455,34 +20443,34 @@
         <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF122" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="AG122" t="n">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="AH122" t="n">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="AI122" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="AJ122" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AK122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL122" t="n">
         <v>0</v>
@@ -20491,87 +20479,87 @@
         <v>0</v>
       </c>
       <c r="AN122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO122" t="n">
         <v>0</v>
       </c>
       <c r="AP122" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR122" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="AS122" t="n">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="AT122" t="n">
-        <v>419</v>
+        <v>185</v>
       </c>
       <c r="AU122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW122" t="n">
         <v>0</v>
       </c>
       <c r="AX122" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>tianfirnanda16@gmail.com</t>
+          <t>tentangsangihe@gmail.com</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>vonnelariunaung77560@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>121</v>
+        <v>225</v>
       </c>
       <c r="J123" t="n">
         <v>1</v>
       </c>
       <c r="K123" t="n">
-        <v>12.5</v>
+        <v>16.67</v>
       </c>
       <c r="L123" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M123" t="n">
         <v>0</v>
@@ -20580,133 +20568,133 @@
         <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P123" t="n">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="Q123" t="n">
-        <v>248.3</v>
+        <v>134.75</v>
       </c>
       <c r="R123" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="S123" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="T123" t="n">
-        <v>7.300000000000001</v>
+        <v>57.46</v>
       </c>
       <c r="U123" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="V123" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="W123" t="n">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="X123" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
       </c>
       <c r="AD123" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="AE123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="AG123" t="n">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="AH123" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="AI123" t="n">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="AJ123" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AK123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM123" t="n">
         <v>0</v>
       </c>
       <c r="AN123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO123" t="n">
         <v>0</v>
       </c>
       <c r="AP123" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR123" t="n">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="AS123" t="n">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="AT123" t="n">
-        <v>432</v>
+        <v>126</v>
       </c>
       <c r="AU123" t="n">
         <v>0</v>
       </c>
       <c r="AV123" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AW123" t="n">
         <v>0</v>
       </c>
       <c r="AX123" t="n">
-        <v>3</v>
+        <v>256</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>tikamustika1704@gmail.com</t>
+          <t>tianfirnanda16@gmail.com</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -20720,64 +20708,64 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="L124" t="n">
+        <v>17</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>3</v>
+      </c>
+      <c r="P124" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>191.79</v>
+      </c>
+      <c r="R124" t="n">
+        <v>49</v>
+      </c>
+      <c r="S124" t="n">
+        <v>1</v>
+      </c>
+      <c r="T124" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U124" t="n">
+        <v>27</v>
+      </c>
+      <c r="V124" t="n">
+        <v>128</v>
+      </c>
+      <c r="W124" t="n">
+        <v>332</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" t="n">
         <v>7</v>
       </c>
-      <c r="M124" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" t="n">
-        <v>18</v>
-      </c>
-      <c r="P124" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>55.59</v>
-      </c>
-      <c r="R124" t="n">
-        <v>42</v>
-      </c>
-      <c r="S124" t="n">
-        <v>8</v>
-      </c>
-      <c r="T124" t="n">
-        <v>18.51</v>
-      </c>
-      <c r="U124" t="n">
-        <v>143</v>
-      </c>
-      <c r="V124" t="n">
-        <v>141</v>
-      </c>
-      <c r="W124" t="n">
-        <v>326</v>
-      </c>
-      <c r="X124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y124" t="n">
-        <v>2</v>
-      </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -20789,31 +20777,31 @@
         <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
       </c>
       <c r="AF124" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AG124" t="n">
         <v>371</v>
       </c>
       <c r="AH124" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="AI124" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AJ124" t="n">
         <v>0</v>
       </c>
       <c r="AK124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AL124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM124" t="n">
         <v>0</v>
@@ -20825,120 +20813,120 @@
         <v>0</v>
       </c>
       <c r="AP124" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AQ124" t="n">
         <v>1</v>
       </c>
       <c r="AR124" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AS124" t="n">
         <v>371</v>
       </c>
       <c r="AT124" t="n">
-        <v>437</v>
+        <v>128</v>
       </c>
       <c r="AU124" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AV124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX124" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>tumpiask@gmail.com</t>
+          <t>tikamustika1704@gmail.com</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G125" t="n">
+        <v>47</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>87</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>7</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>18</v>
+      </c>
+      <c r="P125" t="n">
         <v>30</v>
       </c>
-      <c r="H125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" t="n">
-        <v>247</v>
-      </c>
-      <c r="J125" t="n">
-        <v>1</v>
-      </c>
-      <c r="K125" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="L125" t="n">
-        <v>15</v>
-      </c>
-      <c r="M125" t="n">
-        <v>0</v>
-      </c>
-      <c r="N125" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" t="n">
-        <v>5</v>
-      </c>
-      <c r="P125" t="n">
-        <v>148</v>
-      </c>
       <c r="Q125" t="n">
-        <v>125.49</v>
+        <v>55.59</v>
       </c>
       <c r="R125" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="S125" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="T125" t="n">
-        <v>79.36</v>
+        <v>18.51</v>
       </c>
       <c r="U125" t="n">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="V125" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="W125" t="n">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="X125" t="n">
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z125" t="n">
         <v>0</v>
@@ -20947,123 +20935,123 @@
         <v>0</v>
       </c>
       <c r="AB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>514</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>371</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>141</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>326</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK125" t="n">
         <v>2</v>
       </c>
-      <c r="AC125" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>79</v>
-      </c>
-      <c r="AE125" t="n">
+      <c r="AL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>44</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>514</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>371</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>141</v>
+      </c>
+      <c r="AU125" t="n">
         <v>2</v>
       </c>
-      <c r="AF125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AG125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI125" t="n">
-        <v>288</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO125" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP125" t="n">
-        <v>79</v>
-      </c>
-      <c r="AQ125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AS125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AT125" t="n">
-        <v>303</v>
-      </c>
-      <c r="AU125" t="n">
-        <v>0</v>
-      </c>
       <c r="AV125" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW125" t="n">
         <v>0</v>
       </c>
       <c r="AX125" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ungkealbert39@gmail.com</t>
+          <t>tumpiask@gmail.com</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>73</v>
+        <v>247</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="L126" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -21072,153 +21060,153 @@
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="P126" t="n">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="Q126" t="n">
-        <v>145.88</v>
+        <v>125.49</v>
       </c>
       <c r="R126" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="T126" t="n">
-        <v>57.78</v>
+        <v>79.36</v>
       </c>
       <c r="U126" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="V126" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
         <v>2</v>
       </c>
-      <c r="Y126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>1</v>
-      </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD126" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="AE126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF126" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="AG126" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="AH126" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AI126" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="AJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN126" t="n">
         <v>2</v>
       </c>
-      <c r="AK126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN126" t="n">
-        <v>1</v>
-      </c>
       <c r="AO126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP126" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR126" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="AS126" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="AT126" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="AU126" t="n">
         <v>0</v>
       </c>
       <c r="AV126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW126" t="n">
         <v>0</v>
       </c>
       <c r="AX126" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>verawaticristylolaroh02@gmail.com</t>
+          <t>ungkealbert39@gmail.com</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -21227,7 +21215,7 @@
         <v>0</v>
       </c>
       <c r="L127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
@@ -21236,153 +21224,153 @@
         <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P127" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="Q127" t="n">
-        <v>75</v>
+        <v>145.88</v>
       </c>
       <c r="R127" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="S127" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="T127" t="n">
-        <v>105.53</v>
+        <v>57.78</v>
       </c>
       <c r="U127" t="n">
-        <v>107</v>
+        <v>34</v>
       </c>
       <c r="V127" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="W127" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="X127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y127" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
       </c>
       <c r="AD127" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF127" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="AG127" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AH127" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AI127" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="AJ127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK127" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AL127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM127" t="n">
         <v>0</v>
       </c>
       <c r="AN127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO127" t="n">
         <v>0</v>
       </c>
       <c r="AP127" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR127" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="AS127" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AT127" t="n">
-        <v>394</v>
+        <v>101</v>
       </c>
       <c r="AU127" t="n">
         <v>0</v>
       </c>
       <c r="AV127" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AW127" t="n">
         <v>0</v>
       </c>
       <c r="AX127" t="n">
-        <v>1</v>
+        <v>306</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>wenaserin@gmail.com</t>
+          <t>verawaticristylolaroh02@gmail.com</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>georgemulersasiangsasiang@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -21391,7 +21379,7 @@
         <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
@@ -21400,40 +21388,40 @@
         <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P128" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q128" t="n">
-        <v>48.71</v>
+        <v>75</v>
       </c>
       <c r="R128" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="S128" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="T128" t="n">
-        <v>34.13</v>
+        <v>105.53</v>
       </c>
       <c r="U128" t="n">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="V128" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="W128" t="n">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="X128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y128" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Z128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -21445,31 +21433,31 @@
         <v>0</v>
       </c>
       <c r="AD128" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="AE128" t="n">
         <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="AG128" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AH128" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="AI128" t="n">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="AJ128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AK128" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AL128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM128" t="n">
         <v>0</v>
@@ -21481,72 +21469,72 @@
         <v>0</v>
       </c>
       <c r="AP128" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="AQ128" t="n">
         <v>0</v>
       </c>
       <c r="AR128" t="n">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="AS128" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AT128" t="n">
-        <v>372</v>
+        <v>142</v>
       </c>
       <c r="AU128" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AV128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW128" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX128" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>windametia67@gmail.com</t>
+          <t>wenaserin@gmail.com</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>manahampijeferson94@gmail.com</t>
+          <t>georgemulersasiangsasiang@gmail.com</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>310</v>
+        <v>38</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -21555,50 +21543,50 @@
         <v>0</v>
       </c>
       <c r="L129" t="n">
+        <v>10</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>19</v>
+      </c>
+      <c r="P129" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="R129" t="n">
+        <v>25</v>
+      </c>
+      <c r="S129" t="n">
+        <v>11</v>
+      </c>
+      <c r="T129" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="U129" t="n">
+        <v>41</v>
+      </c>
+      <c r="V129" t="n">
+        <v>131</v>
+      </c>
+      <c r="W129" t="n">
+        <v>317</v>
+      </c>
+      <c r="X129" t="n">
         <v>5</v>
       </c>
-      <c r="M129" t="n">
-        <v>0</v>
-      </c>
-      <c r="N129" t="n">
-        <v>0</v>
-      </c>
-      <c r="O129" t="n">
+      <c r="Y129" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z129" t="n">
         <v>2</v>
       </c>
-      <c r="P129" t="n">
-        <v>79</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>118.15</v>
-      </c>
-      <c r="R129" t="n">
-        <v>74</v>
-      </c>
-      <c r="S129" t="n">
-        <v>24</v>
-      </c>
-      <c r="T129" t="n">
-        <v>32.66</v>
-      </c>
-      <c r="U129" t="n">
-        <v>80</v>
-      </c>
-      <c r="V129" t="n">
-        <v>59</v>
-      </c>
-      <c r="W129" t="n">
-        <v>187</v>
-      </c>
-      <c r="X129" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>3</v>
-      </c>
       <c r="AA129" t="n">
         <v>0</v>
       </c>
@@ -21609,88 +21597,88 @@
         <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="AE129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF129" t="n">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="AG129" t="n">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="AH129" t="n">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="AI129" t="n">
-        <v>189</v>
+        <v>317</v>
       </c>
       <c r="AJ129" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AK129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AL129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM129" t="n">
         <v>0</v>
       </c>
       <c r="AN129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO129" t="n">
         <v>0</v>
       </c>
       <c r="AP129" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="AQ129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR129" t="n">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="AS129" t="n">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="AT129" t="n">
-        <v>313</v>
+        <v>131</v>
       </c>
       <c r="AU129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AV129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX129" t="n">
-        <v>1</v>
+        <v>317</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ybawembang@gmail.com</t>
+          <t>windametia67@gmail.com</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>manahampijeferson94@gmail.com</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -21704,13 +21692,13 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -21719,7 +21707,7 @@
         <v>0</v>
       </c>
       <c r="L130" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="M130" t="n">
         <v>0</v>
@@ -21728,40 +21716,40 @@
         <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="P130" t="n">
-        <v>191</v>
+        <v>79</v>
       </c>
       <c r="Q130" t="n">
-        <v>269.56</v>
+        <v>118.15</v>
       </c>
       <c r="R130" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="S130" t="n">
+        <v>24</v>
+      </c>
+      <c r="T130" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="U130" t="n">
+        <v>80</v>
+      </c>
+      <c r="V130" t="n">
+        <v>59</v>
+      </c>
+      <c r="W130" t="n">
+        <v>187</v>
+      </c>
+      <c r="X130" t="n">
         <v>9</v>
       </c>
-      <c r="T130" t="n">
-        <v>21.84</v>
-      </c>
-      <c r="U130" t="n">
-        <v>12</v>
-      </c>
-      <c r="V130" t="n">
-        <v>61</v>
-      </c>
-      <c r="W130" t="n">
-        <v>307</v>
-      </c>
-      <c r="X130" t="n">
-        <v>1</v>
-      </c>
       <c r="Y130" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -21773,28 +21761,28 @@
         <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="AE130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF130" t="n">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AG130" t="n">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="AH130" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AI130" t="n">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="AJ130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AK130" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="AL130" t="n">
         <v>0</v>
@@ -21803,78 +21791,78 @@
         <v>0</v>
       </c>
       <c r="AN130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO130" t="n">
         <v>0</v>
       </c>
       <c r="AP130" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AR130" t="n">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AS130" t="n">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="AT130" t="n">
-        <v>386</v>
+        <v>59</v>
       </c>
       <c r="AU130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV130" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AW130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX130" t="n">
-        <v>1</v>
+        <v>187</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>yudhistiratangkabiringan@gmail.com</t>
+          <t>ybawembang@gmail.com</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>145</v>
+        <v>309</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -21883,7 +21871,7 @@
         <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="M131" t="n">
         <v>0</v>
@@ -21892,37 +21880,37 @@
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P131" t="n">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="Q131" t="n">
-        <v>90.86</v>
+        <v>269.56</v>
       </c>
       <c r="R131" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="S131" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T131" t="n">
-        <v>38.52</v>
+        <v>21.84</v>
       </c>
       <c r="U131" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="V131" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="W131" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="X131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="Z131" t="n">
         <v>0</v>
@@ -21937,28 +21925,28 @@
         <v>0</v>
       </c>
       <c r="AD131" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AE131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF131" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="AG131" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="AH131" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="AI131" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="AJ131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AK131" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AL131" t="n">
         <v>0</v>
@@ -21973,72 +21961,72 @@
         <v>0</v>
       </c>
       <c r="AP131" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR131" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="AS131" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="AT131" t="n">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="AU131" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="AV131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW131" t="n">
         <v>0</v>
       </c>
       <c r="AX131" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>yustindurian@gmail.com</t>
+          <t>yudhistiratangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>fianemansauda89@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>287</v>
+        <v>145</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -22050,118 +22038,282 @@
         <v>5</v>
       </c>
       <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>4</v>
+      </c>
+      <c r="P132" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>90.86</v>
+      </c>
+      <c r="R132" t="n">
+        <v>59</v>
+      </c>
+      <c r="S132" t="n">
+        <v>16</v>
+      </c>
+      <c r="T132" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="U132" t="n">
+        <v>54</v>
+      </c>
+      <c r="V132" t="n">
+        <v>139</v>
+      </c>
+      <c r="W132" t="n">
+        <v>209</v>
+      </c>
+      <c r="X132" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>400</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>261</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>139</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>209</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>46</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>400</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>261</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>139</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Yustin Durian</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>yustindurian@gmail.com</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Fiane Greti Mansauda</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>fianemansauda89@gmail.com</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>(070) TABUKAN TENGAH</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Kharis</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>24</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>287</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>5</v>
+      </c>
+      <c r="M133" t="n">
         <v>2</v>
       </c>
-      <c r="N132" t="n">
+      <c r="N133" t="n">
         <v>47.62</v>
       </c>
-      <c r="O132" t="n">
+      <c r="O133" t="n">
         <v>10</v>
       </c>
-      <c r="P132" t="n">
+      <c r="P133" t="n">
         <v>84</v>
       </c>
-      <c r="Q132" t="n">
+      <c r="Q133" t="n">
         <v>159.3</v>
       </c>
-      <c r="R132" t="n">
+      <c r="R133" t="n">
         <v>67</v>
       </c>
-      <c r="S132" t="n">
+      <c r="S133" t="n">
         <v>12</v>
       </c>
-      <c r="T132" t="n">
+      <c r="T133" t="n">
         <v>15.38</v>
       </c>
-      <c r="U132" t="n">
+      <c r="U133" t="n">
         <v>68</v>
       </c>
-      <c r="V132" t="n">
+      <c r="V133" t="n">
         <v>131</v>
       </c>
-      <c r="W132" t="n">
+      <c r="W133" t="n">
         <v>278</v>
       </c>
-      <c r="X132" t="n">
+      <c r="X133" t="n">
         <v>2</v>
       </c>
-      <c r="Y132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD132" t="n">
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
         <v>43</v>
       </c>
-      <c r="AE132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF132" t="n">
+      <c r="AE133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF133" t="n">
         <v>456</v>
       </c>
-      <c r="AG132" t="n">
+      <c r="AG133" t="n">
         <v>325</v>
       </c>
-      <c r="AH132" t="n">
+      <c r="AH133" t="n">
         <v>131</v>
       </c>
-      <c r="AI132" t="n">
+      <c r="AI133" t="n">
         <v>278</v>
       </c>
-      <c r="AJ132" t="n">
+      <c r="AJ133" t="n">
         <v>2</v>
       </c>
-      <c r="AK132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP132" t="n">
+      <c r="AK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP133" t="n">
         <v>43</v>
       </c>
-      <c r="AQ132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR132" t="n">
+      <c r="AQ133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR133" t="n">
         <v>456</v>
       </c>
-      <c r="AS132" t="n">
+      <c r="AS133" t="n">
         <v>325</v>
       </c>
-      <c r="AT132" t="n">
-        <v>368</v>
-      </c>
-      <c r="AU132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV132" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX132" t="n">
-        <v>0</v>
+      <c r="AT133" t="n">
+        <v>131</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
